--- a/jogos_2026-10-15.xlsx
+++ b/jogos_2026-10-15.xlsx
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Muğlaspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Muğlaspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G13">

--- a/jogos_2026-10-15.xlsx
+++ b/jogos_2026-10-15.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G3">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G4">

--- a/jogos_2026-10-15.xlsx
+++ b/jogos_2026-10-15.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU19"/>
+  <dimension ref="A1:AU34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1082,22 +1082,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="G5">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G6">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N6">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G7">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N7">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-10-15 11:50:00</t>
+          <t>2026-10-15 11:00:00</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G8">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-10-15 12:00:00</t>
+          <t>2026-10-15 11:00:00</t>
         </is>
       </c>
     </row>
@@ -1729,12 +1729,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G9">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-10-15 12:15:00</t>
+          <t>2026-10-15 11:00:00</t>
         </is>
       </c>
     </row>
@@ -1892,27 +1892,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G10">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-10-15 13:00:00</t>
+          <t>2026-10-15 11:00:00</t>
         </is>
       </c>
     </row>
@@ -2055,12 +2055,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G11">
@@ -2098,68 +2098,68 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N11">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O11">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="R11">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="V11">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X11">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y11">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z11">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA11">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC11">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD11">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE11">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG11">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AK11">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-10-15 13:30:00</t>
+          <t>2026-10-15 11:00:00</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Muğlaspor</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G12">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-10-15 14:00:00</t>
+          <t>2026-10-15 11:00:00</t>
         </is>
       </c>
     </row>
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G13">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-10-15 14:00:00</t>
+          <t>2026-10-15 11:00:00</t>
         </is>
       </c>
     </row>
@@ -2544,12 +2544,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="G14">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-10-15 15:00:00</t>
+          <t>2026-10-15 11:00:00</t>
         </is>
       </c>
     </row>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G15">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-10-15 15:45:00</t>
+          <t>2026-10-15 11:00:00</t>
         </is>
       </c>
     </row>
@@ -2870,12 +2870,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G16">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-10-15 16:00:00</t>
+          <t>2026-10-15 11:00:00</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="G17">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2026-10-15 17:30:00</t>
+          <t>2026-10-15 11:00:00</t>
         </is>
       </c>
     </row>
@@ -3196,12 +3196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G18">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N18">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2026-10-15 21:00:00</t>
+          <t>2026-10-15 11:00:00</t>
         </is>
       </c>
     </row>
@@ -3359,156 +3359,2601 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>MC Alger</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>USM Khenchela</t>
+        </is>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>-1</v>
+      </c>
+      <c r="AN19">
+        <v>-1</v>
+      </c>
+      <c r="AO19">
+        <v>-1</v>
+      </c>
+      <c r="AP19">
+        <v>-1</v>
+      </c>
+      <c r="AQ19">
+        <v>0</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>0</v>
+      </c>
+      <c r="AT19">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2026-10-15 11:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Latvia Virsliga</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Rīgas FS</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Super Nova</t>
+        </is>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0</v>
+      </c>
+      <c r="AG20">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
+        <v>0</v>
+      </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>-1</v>
+      </c>
+      <c r="AN20">
+        <v>-1</v>
+      </c>
+      <c r="AO20">
+        <v>-1</v>
+      </c>
+      <c r="AP20">
+        <v>-1</v>
+      </c>
+      <c r="AQ20">
+        <v>0</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2026-10-15 11:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Turkey 1. Lig</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Mardin BB</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Fatih Karagümrük</t>
+        </is>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
+        <v>0</v>
+      </c>
+      <c r="AK21">
+        <v>0</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>-1</v>
+      </c>
+      <c r="AN21">
+        <v>-1</v>
+      </c>
+      <c r="AO21">
+        <v>-1</v>
+      </c>
+      <c r="AP21">
+        <v>-1</v>
+      </c>
+      <c r="AQ21">
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>0</v>
+      </c>
+      <c r="AT21">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2026-10-15 11:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Professional League</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Al Khaleej</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Al Feiha</t>
+        </is>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
+        <v>0</v>
+      </c>
+      <c r="AK22">
+        <v>0</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>-1</v>
+      </c>
+      <c r="AN22">
+        <v>-1</v>
+      </c>
+      <c r="AO22">
+        <v>-1</v>
+      </c>
+      <c r="AP22">
+        <v>-1</v>
+      </c>
+      <c r="AQ22">
+        <v>0</v>
+      </c>
+      <c r="AR22">
+        <v>0</v>
+      </c>
+      <c r="AS22">
+        <v>0</v>
+      </c>
+      <c r="AT22">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>2026-10-15 11:50:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Jordan Jordanian Pro League</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Al Arabi</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Shabab Al Ordon</t>
+        </is>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
+        <v>0</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>-1</v>
+      </c>
+      <c r="AN23">
+        <v>-1</v>
+      </c>
+      <c r="AO23">
+        <v>-1</v>
+      </c>
+      <c r="AP23">
+        <v>-1</v>
+      </c>
+      <c r="AQ23">
+        <v>0</v>
+      </c>
+      <c r="AR23">
+        <v>0</v>
+      </c>
+      <c r="AS23">
+        <v>0</v>
+      </c>
+      <c r="AT23">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Professional League</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Al Hazm</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Al Fateh</t>
+        </is>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>0</v>
+      </c>
+      <c r="AG24">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24">
+        <v>0</v>
+      </c>
+      <c r="AK24">
+        <v>0</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>-1</v>
+      </c>
+      <c r="AN24">
+        <v>-1</v>
+      </c>
+      <c r="AO24">
+        <v>-1</v>
+      </c>
+      <c r="AP24">
+        <v>-1</v>
+      </c>
+      <c r="AQ24">
+        <v>0</v>
+      </c>
+      <c r="AR24">
+        <v>0</v>
+      </c>
+      <c r="AS24">
+        <v>0</v>
+      </c>
+      <c r="AT24">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:15:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Estonia Meistriliiga</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Tallinna FC Flora</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tallinna FC Levadia</t>
+        </is>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>0</v>
+      </c>
+      <c r="AG25">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
+        <v>0</v>
+      </c>
+      <c r="AK25">
+        <v>0</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>-1</v>
+      </c>
+      <c r="AN25">
+        <v>-1</v>
+      </c>
+      <c r="AO25">
+        <v>-1</v>
+      </c>
+      <c r="AP25">
+        <v>-1</v>
+      </c>
+      <c r="AQ25">
+        <v>0</v>
+      </c>
+      <c r="AR25">
+        <v>0</v>
+      </c>
+      <c r="AS25">
+        <v>0</v>
+      </c>
+      <c r="AT25">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>2026-10-15 13:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Poland 1. Liga</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Pogoń Siedlce</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Puszcza Niepołomice</t>
+        </is>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N26">
+        <v>2.94</v>
+      </c>
+      <c r="O26">
+        <v>3.05</v>
+      </c>
+      <c r="P26">
+        <v>2.4</v>
+      </c>
+      <c r="Q26">
+        <v>3.57</v>
+      </c>
+      <c r="R26">
+        <v>2.01</v>
+      </c>
+      <c r="S26">
+        <v>1.42</v>
+      </c>
+      <c r="T26">
+        <v>2.59</v>
+      </c>
+      <c r="U26">
+        <v>3.12</v>
+      </c>
+      <c r="V26">
+        <v>1.36</v>
+      </c>
+      <c r="W26">
+        <v>1.06</v>
+      </c>
+      <c r="X26">
+        <v>1.04</v>
+      </c>
+      <c r="Y26">
+        <v>1.31</v>
+      </c>
+      <c r="Z26">
+        <v>2.92</v>
+      </c>
+      <c r="AA26">
+        <v>2.03</v>
+      </c>
+      <c r="AB26">
+        <v>1.7</v>
+      </c>
+      <c r="AC26">
+        <v>3.42</v>
+      </c>
+      <c r="AD26">
+        <v>1.22</v>
+      </c>
+      <c r="AE26">
+        <v>1.05</v>
+      </c>
+      <c r="AF26">
+        <v>1.78</v>
+      </c>
+      <c r="AG26">
+        <v>1.91</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
+        <v>1.55</v>
+      </c>
+      <c r="AK26">
+        <v>1.3</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>-1</v>
+      </c>
+      <c r="AN26">
+        <v>-1</v>
+      </c>
+      <c r="AO26">
+        <v>-1</v>
+      </c>
+      <c r="AP26">
+        <v>-1</v>
+      </c>
+      <c r="AQ26">
+        <v>0</v>
+      </c>
+      <c r="AR26">
+        <v>0</v>
+      </c>
+      <c r="AS26">
+        <v>0</v>
+      </c>
+      <c r="AT26">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>2026-10-15 13:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Turkey 1. Lig</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Muğlaspor</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Bursaspor</t>
+        </is>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0</v>
+      </c>
+      <c r="AC27">
+        <v>0</v>
+      </c>
+      <c r="AD27">
+        <v>0</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>0</v>
+      </c>
+      <c r="AG27">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
+        <v>0</v>
+      </c>
+      <c r="AK27">
+        <v>0</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>-1</v>
+      </c>
+      <c r="AN27">
+        <v>-1</v>
+      </c>
+      <c r="AO27">
+        <v>-1</v>
+      </c>
+      <c r="AP27">
+        <v>-1</v>
+      </c>
+      <c r="AQ27">
+        <v>0</v>
+      </c>
+      <c r="AR27">
+        <v>0</v>
+      </c>
+      <c r="AS27">
+        <v>0</v>
+      </c>
+      <c r="AT27">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Turkey 1. Lig</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Manisa BBSK</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Erokspor</t>
+        </is>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>0</v>
+      </c>
+      <c r="AG28">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
+        <v>0</v>
+      </c>
+      <c r="AK28">
+        <v>0</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>-1</v>
+      </c>
+      <c r="AN28">
+        <v>-1</v>
+      </c>
+      <c r="AO28">
+        <v>-1</v>
+      </c>
+      <c r="AP28">
+        <v>-1</v>
+      </c>
+      <c r="AQ28">
+        <v>0</v>
+      </c>
+      <c r="AR28">
+        <v>0</v>
+      </c>
+      <c r="AS28">
+        <v>0</v>
+      </c>
+      <c r="AT28">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>2026-10-15 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Professional League</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Al Ahli</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Al Nassr</t>
+        </is>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>0</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
+        <v>0</v>
+      </c>
+      <c r="AC29">
+        <v>0</v>
+      </c>
+      <c r="AD29">
+        <v>0</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>0</v>
+      </c>
+      <c r="AG29">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29">
+        <v>0</v>
+      </c>
+      <c r="AK29">
+        <v>0</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>-1</v>
+      </c>
+      <c r="AN29">
+        <v>-1</v>
+      </c>
+      <c r="AO29">
+        <v>-1</v>
+      </c>
+      <c r="AP29">
+        <v>-1</v>
+      </c>
+      <c r="AQ29">
+        <v>0</v>
+      </c>
+      <c r="AR29">
+        <v>0</v>
+      </c>
+      <c r="AS29">
+        <v>0</v>
+      </c>
+      <c r="AT29">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>2026-10-15 15:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>France National</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Caen</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>La Roche VF</t>
+        </is>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>0</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>0</v>
+      </c>
+      <c r="X30">
+        <v>0</v>
+      </c>
+      <c r="Y30">
+        <v>0</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+      <c r="AA30">
+        <v>0</v>
+      </c>
+      <c r="AB30">
+        <v>0</v>
+      </c>
+      <c r="AC30">
+        <v>0</v>
+      </c>
+      <c r="AD30">
+        <v>0</v>
+      </c>
+      <c r="AE30">
+        <v>0</v>
+      </c>
+      <c r="AF30">
+        <v>0</v>
+      </c>
+      <c r="AG30">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
+        <v>0</v>
+      </c>
+      <c r="AK30">
+        <v>0</v>
+      </c>
+      <c r="AL30">
+        <v>0</v>
+      </c>
+      <c r="AM30">
+        <v>-1</v>
+      </c>
+      <c r="AN30">
+        <v>-1</v>
+      </c>
+      <c r="AO30">
+        <v>-1</v>
+      </c>
+      <c r="AP30">
+        <v>-1</v>
+      </c>
+      <c r="AQ30">
+        <v>0</v>
+      </c>
+      <c r="AR30">
+        <v>0</v>
+      </c>
+      <c r="AS30">
+        <v>0</v>
+      </c>
+      <c r="AT30">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>2026-10-15 15:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>England EFL League One</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Mansfield Town</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Oxford United</t>
+        </is>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>0</v>
+      </c>
+      <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>0</v>
+      </c>
+      <c r="X31">
+        <v>0</v>
+      </c>
+      <c r="Y31">
+        <v>0</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+      <c r="AA31">
+        <v>0</v>
+      </c>
+      <c r="AB31">
+        <v>0</v>
+      </c>
+      <c r="AC31">
+        <v>0</v>
+      </c>
+      <c r="AD31">
+        <v>0</v>
+      </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <v>0</v>
+      </c>
+      <c r="AG31">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31">
+        <v>0</v>
+      </c>
+      <c r="AK31">
+        <v>0</v>
+      </c>
+      <c r="AL31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>-1</v>
+      </c>
+      <c r="AN31">
+        <v>-1</v>
+      </c>
+      <c r="AO31">
+        <v>-1</v>
+      </c>
+      <c r="AP31">
+        <v>-1</v>
+      </c>
+      <c r="AQ31">
+        <v>0</v>
+      </c>
+      <c r="AR31">
+        <v>0</v>
+      </c>
+      <c r="AS31">
+        <v>0</v>
+      </c>
+      <c r="AT31">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>2026-10-15 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Cavalier</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Portmore United</t>
+        </is>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0</v>
+      </c>
+      <c r="X32">
+        <v>0</v>
+      </c>
+      <c r="Y32">
+        <v>0</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+      <c r="AA32">
+        <v>0</v>
+      </c>
+      <c r="AB32">
+        <v>0</v>
+      </c>
+      <c r="AC32">
+        <v>0</v>
+      </c>
+      <c r="AD32">
+        <v>0</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>0</v>
+      </c>
+      <c r="AG32">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32">
+        <v>0</v>
+      </c>
+      <c r="AK32">
+        <v>0</v>
+      </c>
+      <c r="AL32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>-1</v>
+      </c>
+      <c r="AN32">
+        <v>-1</v>
+      </c>
+      <c r="AO32">
+        <v>-1</v>
+      </c>
+      <c r="AP32">
+        <v>-1</v>
+      </c>
+      <c r="AQ32">
+        <v>0</v>
+      </c>
+      <c r="AR32">
+        <v>0</v>
+      </c>
+      <c r="AS32">
+        <v>0</v>
+      </c>
+      <c r="AT32">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>2026-10-15 17:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>2026/2027</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Welwalo Adigrat Uni</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Fasil Ketema</t>
+        </is>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <v>0</v>
+      </c>
+      <c r="R33">
+        <v>0</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
+      <c r="U33">
+        <v>0</v>
+      </c>
+      <c r="V33">
+        <v>0</v>
+      </c>
+      <c r="W33">
+        <v>0</v>
+      </c>
+      <c r="X33">
+        <v>0</v>
+      </c>
+      <c r="Y33">
+        <v>0</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+      <c r="AA33">
+        <v>0</v>
+      </c>
+      <c r="AB33">
+        <v>0</v>
+      </c>
+      <c r="AC33">
+        <v>0</v>
+      </c>
+      <c r="AD33">
+        <v>0</v>
+      </c>
+      <c r="AE33">
+        <v>0</v>
+      </c>
+      <c r="AF33">
+        <v>0</v>
+      </c>
+      <c r="AG33">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ33">
+        <v>0</v>
+      </c>
+      <c r="AK33">
+        <v>0</v>
+      </c>
+      <c r="AL33">
+        <v>0</v>
+      </c>
+      <c r="AM33">
+        <v>-1</v>
+      </c>
+      <c r="AN33">
+        <v>-1</v>
+      </c>
+      <c r="AO33">
+        <v>-1</v>
+      </c>
+      <c r="AP33">
+        <v>-1</v>
+      </c>
+      <c r="AQ33">
+        <v>0</v>
+      </c>
+      <c r="AR33">
+        <v>0</v>
+      </c>
+      <c r="AS33">
+        <v>0</v>
+      </c>
+      <c r="AT33">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>2026-10-15 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ethiopia Ethiopia Premier League</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
         <is>
           <t>Gamo Chencha</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Sidama Bunna</t>
         </is>
       </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19" t="inlineStr">
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t>suspended</t>
         </is>
       </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19">
-        <v>0</v>
-      </c>
-      <c r="P19">
-        <v>0</v>
-      </c>
-      <c r="Q19">
-        <v>0</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
-        <v>0</v>
-      </c>
-      <c r="T19">
-        <v>0</v>
-      </c>
-      <c r="U19">
-        <v>0</v>
-      </c>
-      <c r="V19">
-        <v>0</v>
-      </c>
-      <c r="W19">
-        <v>0</v>
-      </c>
-      <c r="X19">
-        <v>0</v>
-      </c>
-      <c r="Y19">
-        <v>0</v>
-      </c>
-      <c r="Z19">
-        <v>0</v>
-      </c>
-      <c r="AA19">
-        <v>0</v>
-      </c>
-      <c r="AB19">
-        <v>0</v>
-      </c>
-      <c r="AC19">
-        <v>0</v>
-      </c>
-      <c r="AD19">
-        <v>0</v>
-      </c>
-      <c r="AE19">
-        <v>0</v>
-      </c>
-      <c r="AF19">
-        <v>0</v>
-      </c>
-      <c r="AG19">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19">
-        <v>0</v>
-      </c>
-      <c r="AK19">
-        <v>0</v>
-      </c>
-      <c r="AL19">
-        <v>0</v>
-      </c>
-      <c r="AM19">
-        <v>-1</v>
-      </c>
-      <c r="AN19">
-        <v>-1</v>
-      </c>
-      <c r="AO19">
-        <v>-1</v>
-      </c>
-      <c r="AP19">
-        <v>-1</v>
-      </c>
-      <c r="AQ19">
-        <v>0</v>
-      </c>
-      <c r="AR19">
-        <v>0</v>
-      </c>
-      <c r="AS19">
-        <v>0</v>
-      </c>
-      <c r="AT19">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>0</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0</v>
+      </c>
+      <c r="X34">
+        <v>0</v>
+      </c>
+      <c r="Y34">
+        <v>0</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+      <c r="AA34">
+        <v>0</v>
+      </c>
+      <c r="AB34">
+        <v>0</v>
+      </c>
+      <c r="AC34">
+        <v>0</v>
+      </c>
+      <c r="AD34">
+        <v>0</v>
+      </c>
+      <c r="AE34">
+        <v>0</v>
+      </c>
+      <c r="AF34">
+        <v>0</v>
+      </c>
+      <c r="AG34">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34">
+        <v>0</v>
+      </c>
+      <c r="AK34">
+        <v>0</v>
+      </c>
+      <c r="AL34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>-1</v>
+      </c>
+      <c r="AN34">
+        <v>-1</v>
+      </c>
+      <c r="AO34">
+        <v>-1</v>
+      </c>
+      <c r="AP34">
+        <v>-1</v>
+      </c>
+      <c r="AQ34">
+        <v>0</v>
+      </c>
+      <c r="AR34">
+        <v>0</v>
+      </c>
+      <c r="AS34">
+        <v>0</v>
+      </c>
+      <c r="AT34">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="inlineStr">
         <is>
           <t>2026-10-15 21:00:00</t>
         </is>

--- a/jogos_2026-10-15.xlsx
+++ b/jogos_2026-10-15.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU34"/>
+  <dimension ref="A1:AU19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1082,22 +1082,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G5">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G6">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N6">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G7">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N7">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-10-15 11:00:00</t>
+          <t>2026-10-15 11:50:00</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G8">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-10-15 11:00:00</t>
+          <t>2026-10-15 12:00:00</t>
         </is>
       </c>
     </row>
@@ -1729,12 +1729,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G9">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-10-15 11:00:00</t>
+          <t>2026-10-15 12:15:00</t>
         </is>
       </c>
     </row>
@@ -1892,27 +1892,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G10">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-10-15 11:00:00</t>
+          <t>2026-10-15 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2055,12 +2055,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G11">
@@ -2098,68 +2098,68 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-10-15 11:00:00</t>
+          <t>2026-10-15 13:30:00</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Muğlaspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="G12">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-10-15 11:00:00</t>
+          <t>2026-10-15 14:00:00</t>
         </is>
       </c>
     </row>
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G13">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-10-15 11:00:00</t>
+          <t>2026-10-15 14:00:00</t>
         </is>
       </c>
     </row>
@@ -2544,12 +2544,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G14">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-10-15 11:00:00</t>
+          <t>2026-10-15 15:00:00</t>
         </is>
       </c>
     </row>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="G15">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-10-15 11:00:00</t>
+          <t>2026-10-15 15:45:00</t>
         </is>
       </c>
     </row>
@@ -2870,12 +2870,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-10-15 11:00:00</t>
+          <t>2026-10-15 16:00:00</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G17">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2026-10-15 11:00:00</t>
+          <t>2026-10-15 17:30:00</t>
         </is>
       </c>
     </row>
@@ -3196,12 +3196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G18">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N18">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2026-10-15 11:00:00</t>
+          <t>2026-10-15 21:00:00</t>
         </is>
       </c>
     </row>
@@ -3359,12 +3359,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Gamo Chencha</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G19">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N19">
@@ -3509,2451 +3509,6 @@
         <v>0</v>
       </c>
       <c r="AU19" t="inlineStr">
-        <is>
-          <t>2026-10-15 11:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Latvia Virsliga</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Rīgas FS</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Super Nova</t>
-        </is>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20">
-        <v>0</v>
-      </c>
-      <c r="P20">
-        <v>0</v>
-      </c>
-      <c r="Q20">
-        <v>0</v>
-      </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20">
-        <v>0</v>
-      </c>
-      <c r="T20">
-        <v>0</v>
-      </c>
-      <c r="U20">
-        <v>0</v>
-      </c>
-      <c r="V20">
-        <v>0</v>
-      </c>
-      <c r="W20">
-        <v>0</v>
-      </c>
-      <c r="X20">
-        <v>0</v>
-      </c>
-      <c r="Y20">
-        <v>0</v>
-      </c>
-      <c r="Z20">
-        <v>0</v>
-      </c>
-      <c r="AA20">
-        <v>0</v>
-      </c>
-      <c r="AB20">
-        <v>0</v>
-      </c>
-      <c r="AC20">
-        <v>0</v>
-      </c>
-      <c r="AD20">
-        <v>0</v>
-      </c>
-      <c r="AE20">
-        <v>0</v>
-      </c>
-      <c r="AF20">
-        <v>0</v>
-      </c>
-      <c r="AG20">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20">
-        <v>0</v>
-      </c>
-      <c r="AK20">
-        <v>0</v>
-      </c>
-      <c r="AL20">
-        <v>0</v>
-      </c>
-      <c r="AM20">
-        <v>-1</v>
-      </c>
-      <c r="AN20">
-        <v>-1</v>
-      </c>
-      <c r="AO20">
-        <v>-1</v>
-      </c>
-      <c r="AP20">
-        <v>-1</v>
-      </c>
-      <c r="AQ20">
-        <v>0</v>
-      </c>
-      <c r="AR20">
-        <v>0</v>
-      </c>
-      <c r="AS20">
-        <v>0</v>
-      </c>
-      <c r="AT20">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>2026-10-15 11:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Turkey 1. Lig</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Mardin BB</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Fatih Karagümrük</t>
-        </is>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
-      <c r="P21">
-        <v>0</v>
-      </c>
-      <c r="Q21">
-        <v>0</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>0</v>
-      </c>
-      <c r="V21">
-        <v>0</v>
-      </c>
-      <c r="W21">
-        <v>0</v>
-      </c>
-      <c r="X21">
-        <v>0</v>
-      </c>
-      <c r="Y21">
-        <v>0</v>
-      </c>
-      <c r="Z21">
-        <v>0</v>
-      </c>
-      <c r="AA21">
-        <v>0</v>
-      </c>
-      <c r="AB21">
-        <v>0</v>
-      </c>
-      <c r="AC21">
-        <v>0</v>
-      </c>
-      <c r="AD21">
-        <v>0</v>
-      </c>
-      <c r="AE21">
-        <v>0</v>
-      </c>
-      <c r="AF21">
-        <v>0</v>
-      </c>
-      <c r="AG21">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21">
-        <v>0</v>
-      </c>
-      <c r="AK21">
-        <v>0</v>
-      </c>
-      <c r="AL21">
-        <v>0</v>
-      </c>
-      <c r="AM21">
-        <v>-1</v>
-      </c>
-      <c r="AN21">
-        <v>-1</v>
-      </c>
-      <c r="AO21">
-        <v>-1</v>
-      </c>
-      <c r="AP21">
-        <v>-1</v>
-      </c>
-      <c r="AQ21">
-        <v>0</v>
-      </c>
-      <c r="AR21">
-        <v>0</v>
-      </c>
-      <c r="AS21">
-        <v>0</v>
-      </c>
-      <c r="AT21">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>2026-10-15 11:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Saudi Arabia Professional League</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Al Khaleej</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Al Feiha</t>
-        </is>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22">
-        <v>0</v>
-      </c>
-      <c r="P22">
-        <v>0</v>
-      </c>
-      <c r="Q22">
-        <v>0</v>
-      </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-      <c r="T22">
-        <v>0</v>
-      </c>
-      <c r="U22">
-        <v>0</v>
-      </c>
-      <c r="V22">
-        <v>0</v>
-      </c>
-      <c r="W22">
-        <v>0</v>
-      </c>
-      <c r="X22">
-        <v>0</v>
-      </c>
-      <c r="Y22">
-        <v>0</v>
-      </c>
-      <c r="Z22">
-        <v>0</v>
-      </c>
-      <c r="AA22">
-        <v>0</v>
-      </c>
-      <c r="AB22">
-        <v>0</v>
-      </c>
-      <c r="AC22">
-        <v>0</v>
-      </c>
-      <c r="AD22">
-        <v>0</v>
-      </c>
-      <c r="AE22">
-        <v>0</v>
-      </c>
-      <c r="AF22">
-        <v>0</v>
-      </c>
-      <c r="AG22">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22">
-        <v>0</v>
-      </c>
-      <c r="AK22">
-        <v>0</v>
-      </c>
-      <c r="AL22">
-        <v>0</v>
-      </c>
-      <c r="AM22">
-        <v>-1</v>
-      </c>
-      <c r="AN22">
-        <v>-1</v>
-      </c>
-      <c r="AO22">
-        <v>-1</v>
-      </c>
-      <c r="AP22">
-        <v>-1</v>
-      </c>
-      <c r="AQ22">
-        <v>0</v>
-      </c>
-      <c r="AR22">
-        <v>0</v>
-      </c>
-      <c r="AS22">
-        <v>0</v>
-      </c>
-      <c r="AT22">
-        <v>0</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>2026-10-15 11:50:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Jordan Jordanian Pro League</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Al Arabi</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Shabab Al Ordon</t>
-        </is>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23">
-        <v>0</v>
-      </c>
-      <c r="P23">
-        <v>0</v>
-      </c>
-      <c r="Q23">
-        <v>0</v>
-      </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-      <c r="S23">
-        <v>0</v>
-      </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
-      <c r="U23">
-        <v>0</v>
-      </c>
-      <c r="V23">
-        <v>0</v>
-      </c>
-      <c r="W23">
-        <v>0</v>
-      </c>
-      <c r="X23">
-        <v>0</v>
-      </c>
-      <c r="Y23">
-        <v>0</v>
-      </c>
-      <c r="Z23">
-        <v>0</v>
-      </c>
-      <c r="AA23">
-        <v>0</v>
-      </c>
-      <c r="AB23">
-        <v>0</v>
-      </c>
-      <c r="AC23">
-        <v>0</v>
-      </c>
-      <c r="AD23">
-        <v>0</v>
-      </c>
-      <c r="AE23">
-        <v>0</v>
-      </c>
-      <c r="AF23">
-        <v>0</v>
-      </c>
-      <c r="AG23">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>0</v>
-      </c>
-      <c r="AK23">
-        <v>0</v>
-      </c>
-      <c r="AL23">
-        <v>0</v>
-      </c>
-      <c r="AM23">
-        <v>-1</v>
-      </c>
-      <c r="AN23">
-        <v>-1</v>
-      </c>
-      <c r="AO23">
-        <v>-1</v>
-      </c>
-      <c r="AP23">
-        <v>-1</v>
-      </c>
-      <c r="AQ23">
-        <v>0</v>
-      </c>
-      <c r="AR23">
-        <v>0</v>
-      </c>
-      <c r="AS23">
-        <v>0</v>
-      </c>
-      <c r="AT23">
-        <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>2026-10-15 12:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Saudi Arabia Professional League</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Al Hazm</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Al Fateh</t>
-        </is>
-      </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24">
-        <v>0</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
-      <c r="O24">
-        <v>0</v>
-      </c>
-      <c r="P24">
-        <v>0</v>
-      </c>
-      <c r="Q24">
-        <v>0</v>
-      </c>
-      <c r="R24">
-        <v>0</v>
-      </c>
-      <c r="S24">
-        <v>0</v>
-      </c>
-      <c r="T24">
-        <v>0</v>
-      </c>
-      <c r="U24">
-        <v>0</v>
-      </c>
-      <c r="V24">
-        <v>0</v>
-      </c>
-      <c r="W24">
-        <v>0</v>
-      </c>
-      <c r="X24">
-        <v>0</v>
-      </c>
-      <c r="Y24">
-        <v>0</v>
-      </c>
-      <c r="Z24">
-        <v>0</v>
-      </c>
-      <c r="AA24">
-        <v>0</v>
-      </c>
-      <c r="AB24">
-        <v>0</v>
-      </c>
-      <c r="AC24">
-        <v>0</v>
-      </c>
-      <c r="AD24">
-        <v>0</v>
-      </c>
-      <c r="AE24">
-        <v>0</v>
-      </c>
-      <c r="AF24">
-        <v>0</v>
-      </c>
-      <c r="AG24">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24">
-        <v>0</v>
-      </c>
-      <c r="AK24">
-        <v>0</v>
-      </c>
-      <c r="AL24">
-        <v>0</v>
-      </c>
-      <c r="AM24">
-        <v>-1</v>
-      </c>
-      <c r="AN24">
-        <v>-1</v>
-      </c>
-      <c r="AO24">
-        <v>-1</v>
-      </c>
-      <c r="AP24">
-        <v>-1</v>
-      </c>
-      <c r="AQ24">
-        <v>0</v>
-      </c>
-      <c r="AR24">
-        <v>0</v>
-      </c>
-      <c r="AS24">
-        <v>0</v>
-      </c>
-      <c r="AT24">
-        <v>0</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>2026-10-15 12:15:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Estonia Meistriliiga</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Tallinna FC Flora</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Tallinna FC Levadia</t>
-        </is>
-      </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25">
-        <v>0</v>
-      </c>
-      <c r="P25">
-        <v>0</v>
-      </c>
-      <c r="Q25">
-        <v>0</v>
-      </c>
-      <c r="R25">
-        <v>0</v>
-      </c>
-      <c r="S25">
-        <v>0</v>
-      </c>
-      <c r="T25">
-        <v>0</v>
-      </c>
-      <c r="U25">
-        <v>0</v>
-      </c>
-      <c r="V25">
-        <v>0</v>
-      </c>
-      <c r="W25">
-        <v>0</v>
-      </c>
-      <c r="X25">
-        <v>0</v>
-      </c>
-      <c r="Y25">
-        <v>0</v>
-      </c>
-      <c r="Z25">
-        <v>0</v>
-      </c>
-      <c r="AA25">
-        <v>0</v>
-      </c>
-      <c r="AB25">
-        <v>0</v>
-      </c>
-      <c r="AC25">
-        <v>0</v>
-      </c>
-      <c r="AD25">
-        <v>0</v>
-      </c>
-      <c r="AE25">
-        <v>0</v>
-      </c>
-      <c r="AF25">
-        <v>0</v>
-      </c>
-      <c r="AG25">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25">
-        <v>0</v>
-      </c>
-      <c r="AK25">
-        <v>0</v>
-      </c>
-      <c r="AL25">
-        <v>0</v>
-      </c>
-      <c r="AM25">
-        <v>-1</v>
-      </c>
-      <c r="AN25">
-        <v>-1</v>
-      </c>
-      <c r="AO25">
-        <v>-1</v>
-      </c>
-      <c r="AP25">
-        <v>-1</v>
-      </c>
-      <c r="AQ25">
-        <v>0</v>
-      </c>
-      <c r="AR25">
-        <v>0</v>
-      </c>
-      <c r="AS25">
-        <v>0</v>
-      </c>
-      <c r="AT25">
-        <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>2026-10-15 13:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Poland 1. Liga</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Pogoń Siedlce</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Puszcza Niepołomice</t>
-        </is>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>suspended</t>
-        </is>
-      </c>
-      <c r="N26">
-        <v>2.94</v>
-      </c>
-      <c r="O26">
-        <v>3.05</v>
-      </c>
-      <c r="P26">
-        <v>2.4</v>
-      </c>
-      <c r="Q26">
-        <v>3.57</v>
-      </c>
-      <c r="R26">
-        <v>2.01</v>
-      </c>
-      <c r="S26">
-        <v>1.42</v>
-      </c>
-      <c r="T26">
-        <v>2.59</v>
-      </c>
-      <c r="U26">
-        <v>3.12</v>
-      </c>
-      <c r="V26">
-        <v>1.36</v>
-      </c>
-      <c r="W26">
-        <v>1.06</v>
-      </c>
-      <c r="X26">
-        <v>1.04</v>
-      </c>
-      <c r="Y26">
-        <v>1.31</v>
-      </c>
-      <c r="Z26">
-        <v>2.92</v>
-      </c>
-      <c r="AA26">
-        <v>2.03</v>
-      </c>
-      <c r="AB26">
-        <v>1.7</v>
-      </c>
-      <c r="AC26">
-        <v>3.42</v>
-      </c>
-      <c r="AD26">
-        <v>1.22</v>
-      </c>
-      <c r="AE26">
-        <v>1.05</v>
-      </c>
-      <c r="AF26">
-        <v>1.78</v>
-      </c>
-      <c r="AG26">
-        <v>1.91</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ26">
-        <v>1.55</v>
-      </c>
-      <c r="AK26">
-        <v>1.3</v>
-      </c>
-      <c r="AL26">
-        <v>0</v>
-      </c>
-      <c r="AM26">
-        <v>-1</v>
-      </c>
-      <c r="AN26">
-        <v>-1</v>
-      </c>
-      <c r="AO26">
-        <v>-1</v>
-      </c>
-      <c r="AP26">
-        <v>-1</v>
-      </c>
-      <c r="AQ26">
-        <v>0</v>
-      </c>
-      <c r="AR26">
-        <v>0</v>
-      </c>
-      <c r="AS26">
-        <v>0</v>
-      </c>
-      <c r="AT26">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>2026-10-15 13:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Turkey 1. Lig</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Muğlaspor</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Bursaspor</t>
-        </is>
-      </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
-      <c r="O27">
-        <v>0</v>
-      </c>
-      <c r="P27">
-        <v>0</v>
-      </c>
-      <c r="Q27">
-        <v>0</v>
-      </c>
-      <c r="R27">
-        <v>0</v>
-      </c>
-      <c r="S27">
-        <v>0</v>
-      </c>
-      <c r="T27">
-        <v>0</v>
-      </c>
-      <c r="U27">
-        <v>0</v>
-      </c>
-      <c r="V27">
-        <v>0</v>
-      </c>
-      <c r="W27">
-        <v>0</v>
-      </c>
-      <c r="X27">
-        <v>0</v>
-      </c>
-      <c r="Y27">
-        <v>0</v>
-      </c>
-      <c r="Z27">
-        <v>0</v>
-      </c>
-      <c r="AA27">
-        <v>0</v>
-      </c>
-      <c r="AB27">
-        <v>0</v>
-      </c>
-      <c r="AC27">
-        <v>0</v>
-      </c>
-      <c r="AD27">
-        <v>0</v>
-      </c>
-      <c r="AE27">
-        <v>0</v>
-      </c>
-      <c r="AF27">
-        <v>0</v>
-      </c>
-      <c r="AG27">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>0</v>
-      </c>
-      <c r="AK27">
-        <v>0</v>
-      </c>
-      <c r="AL27">
-        <v>0</v>
-      </c>
-      <c r="AM27">
-        <v>-1</v>
-      </c>
-      <c r="AN27">
-        <v>-1</v>
-      </c>
-      <c r="AO27">
-        <v>-1</v>
-      </c>
-      <c r="AP27">
-        <v>-1</v>
-      </c>
-      <c r="AQ27">
-        <v>0</v>
-      </c>
-      <c r="AR27">
-        <v>0</v>
-      </c>
-      <c r="AS27">
-        <v>0</v>
-      </c>
-      <c r="AT27">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>2026-10-15 14:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Turkey 1. Lig</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Manisa BBSK</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Erokspor</t>
-        </is>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
-      <c r="O28">
-        <v>0</v>
-      </c>
-      <c r="P28">
-        <v>0</v>
-      </c>
-      <c r="Q28">
-        <v>0</v>
-      </c>
-      <c r="R28">
-        <v>0</v>
-      </c>
-      <c r="S28">
-        <v>0</v>
-      </c>
-      <c r="T28">
-        <v>0</v>
-      </c>
-      <c r="U28">
-        <v>0</v>
-      </c>
-      <c r="V28">
-        <v>0</v>
-      </c>
-      <c r="W28">
-        <v>0</v>
-      </c>
-      <c r="X28">
-        <v>0</v>
-      </c>
-      <c r="Y28">
-        <v>0</v>
-      </c>
-      <c r="Z28">
-        <v>0</v>
-      </c>
-      <c r="AA28">
-        <v>0</v>
-      </c>
-      <c r="AB28">
-        <v>0</v>
-      </c>
-      <c r="AC28">
-        <v>0</v>
-      </c>
-      <c r="AD28">
-        <v>0</v>
-      </c>
-      <c r="AE28">
-        <v>0</v>
-      </c>
-      <c r="AF28">
-        <v>0</v>
-      </c>
-      <c r="AG28">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>0</v>
-      </c>
-      <c r="AK28">
-        <v>0</v>
-      </c>
-      <c r="AL28">
-        <v>0</v>
-      </c>
-      <c r="AM28">
-        <v>-1</v>
-      </c>
-      <c r="AN28">
-        <v>-1</v>
-      </c>
-      <c r="AO28">
-        <v>-1</v>
-      </c>
-      <c r="AP28">
-        <v>-1</v>
-      </c>
-      <c r="AQ28">
-        <v>0</v>
-      </c>
-      <c r="AR28">
-        <v>0</v>
-      </c>
-      <c r="AS28">
-        <v>0</v>
-      </c>
-      <c r="AT28">
-        <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>2026-10-15 14:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Saudi Arabia Professional League</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Al Ahli</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Al Nassr</t>
-        </is>
-      </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29">
-        <v>0</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N29">
-        <v>0</v>
-      </c>
-      <c r="O29">
-        <v>0</v>
-      </c>
-      <c r="P29">
-        <v>0</v>
-      </c>
-      <c r="Q29">
-        <v>0</v>
-      </c>
-      <c r="R29">
-        <v>0</v>
-      </c>
-      <c r="S29">
-        <v>0</v>
-      </c>
-      <c r="T29">
-        <v>0</v>
-      </c>
-      <c r="U29">
-        <v>0</v>
-      </c>
-      <c r="V29">
-        <v>0</v>
-      </c>
-      <c r="W29">
-        <v>0</v>
-      </c>
-      <c r="X29">
-        <v>0</v>
-      </c>
-      <c r="Y29">
-        <v>0</v>
-      </c>
-      <c r="Z29">
-        <v>0</v>
-      </c>
-      <c r="AA29">
-        <v>0</v>
-      </c>
-      <c r="AB29">
-        <v>0</v>
-      </c>
-      <c r="AC29">
-        <v>0</v>
-      </c>
-      <c r="AD29">
-        <v>0</v>
-      </c>
-      <c r="AE29">
-        <v>0</v>
-      </c>
-      <c r="AF29">
-        <v>0</v>
-      </c>
-      <c r="AG29">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29">
-        <v>0</v>
-      </c>
-      <c r="AK29">
-        <v>0</v>
-      </c>
-      <c r="AL29">
-        <v>0</v>
-      </c>
-      <c r="AM29">
-        <v>-1</v>
-      </c>
-      <c r="AN29">
-        <v>-1</v>
-      </c>
-      <c r="AO29">
-        <v>-1</v>
-      </c>
-      <c r="AP29">
-        <v>-1</v>
-      </c>
-      <c r="AQ29">
-        <v>0</v>
-      </c>
-      <c r="AR29">
-        <v>0</v>
-      </c>
-      <c r="AS29">
-        <v>0</v>
-      </c>
-      <c r="AT29">
-        <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>2026-10-15 15:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>France National</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Caen</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>La Roche VF</t>
-        </is>
-      </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <v>0</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30">
-        <v>0</v>
-      </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
-      <c r="O30">
-        <v>0</v>
-      </c>
-      <c r="P30">
-        <v>0</v>
-      </c>
-      <c r="Q30">
-        <v>0</v>
-      </c>
-      <c r="R30">
-        <v>0</v>
-      </c>
-      <c r="S30">
-        <v>0</v>
-      </c>
-      <c r="T30">
-        <v>0</v>
-      </c>
-      <c r="U30">
-        <v>0</v>
-      </c>
-      <c r="V30">
-        <v>0</v>
-      </c>
-      <c r="W30">
-        <v>0</v>
-      </c>
-      <c r="X30">
-        <v>0</v>
-      </c>
-      <c r="Y30">
-        <v>0</v>
-      </c>
-      <c r="Z30">
-        <v>0</v>
-      </c>
-      <c r="AA30">
-        <v>0</v>
-      </c>
-      <c r="AB30">
-        <v>0</v>
-      </c>
-      <c r="AC30">
-        <v>0</v>
-      </c>
-      <c r="AD30">
-        <v>0</v>
-      </c>
-      <c r="AE30">
-        <v>0</v>
-      </c>
-      <c r="AF30">
-        <v>0</v>
-      </c>
-      <c r="AG30">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30">
-        <v>0</v>
-      </c>
-      <c r="AK30">
-        <v>0</v>
-      </c>
-      <c r="AL30">
-        <v>0</v>
-      </c>
-      <c r="AM30">
-        <v>-1</v>
-      </c>
-      <c r="AN30">
-        <v>-1</v>
-      </c>
-      <c r="AO30">
-        <v>-1</v>
-      </c>
-      <c r="AP30">
-        <v>-1</v>
-      </c>
-      <c r="AQ30">
-        <v>0</v>
-      </c>
-      <c r="AR30">
-        <v>0</v>
-      </c>
-      <c r="AS30">
-        <v>0</v>
-      </c>
-      <c r="AT30">
-        <v>0</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>2026-10-15 15:45:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>England EFL League One</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Mansfield Town</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Oxford United</t>
-        </is>
-      </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
-      <c r="H31">
-        <v>0</v>
-      </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31">
-        <v>0</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N31">
-        <v>0</v>
-      </c>
-      <c r="O31">
-        <v>0</v>
-      </c>
-      <c r="P31">
-        <v>0</v>
-      </c>
-      <c r="Q31">
-        <v>0</v>
-      </c>
-      <c r="R31">
-        <v>0</v>
-      </c>
-      <c r="S31">
-        <v>0</v>
-      </c>
-      <c r="T31">
-        <v>0</v>
-      </c>
-      <c r="U31">
-        <v>0</v>
-      </c>
-      <c r="V31">
-        <v>0</v>
-      </c>
-      <c r="W31">
-        <v>0</v>
-      </c>
-      <c r="X31">
-        <v>0</v>
-      </c>
-      <c r="Y31">
-        <v>0</v>
-      </c>
-      <c r="Z31">
-        <v>0</v>
-      </c>
-      <c r="AA31">
-        <v>0</v>
-      </c>
-      <c r="AB31">
-        <v>0</v>
-      </c>
-      <c r="AC31">
-        <v>0</v>
-      </c>
-      <c r="AD31">
-        <v>0</v>
-      </c>
-      <c r="AE31">
-        <v>0</v>
-      </c>
-      <c r="AF31">
-        <v>0</v>
-      </c>
-      <c r="AG31">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31">
-        <v>0</v>
-      </c>
-      <c r="AK31">
-        <v>0</v>
-      </c>
-      <c r="AL31">
-        <v>0</v>
-      </c>
-      <c r="AM31">
-        <v>-1</v>
-      </c>
-      <c r="AN31">
-        <v>-1</v>
-      </c>
-      <c r="AO31">
-        <v>-1</v>
-      </c>
-      <c r="AP31">
-        <v>-1</v>
-      </c>
-      <c r="AQ31">
-        <v>0</v>
-      </c>
-      <c r="AR31">
-        <v>0</v>
-      </c>
-      <c r="AS31">
-        <v>0</v>
-      </c>
-      <c r="AT31">
-        <v>0</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>2026-10-15 16:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Cavalier</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Portmore United</t>
-        </is>
-      </c>
-      <c r="G32">
-        <v>0</v>
-      </c>
-      <c r="H32">
-        <v>0</v>
-      </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
-      <c r="J32">
-        <v>0</v>
-      </c>
-      <c r="K32">
-        <v>0</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32">
-        <v>0</v>
-      </c>
-      <c r="P32">
-        <v>0</v>
-      </c>
-      <c r="Q32">
-        <v>0</v>
-      </c>
-      <c r="R32">
-        <v>0</v>
-      </c>
-      <c r="S32">
-        <v>0</v>
-      </c>
-      <c r="T32">
-        <v>0</v>
-      </c>
-      <c r="U32">
-        <v>0</v>
-      </c>
-      <c r="V32">
-        <v>0</v>
-      </c>
-      <c r="W32">
-        <v>0</v>
-      </c>
-      <c r="X32">
-        <v>0</v>
-      </c>
-      <c r="Y32">
-        <v>0</v>
-      </c>
-      <c r="Z32">
-        <v>0</v>
-      </c>
-      <c r="AA32">
-        <v>0</v>
-      </c>
-      <c r="AB32">
-        <v>0</v>
-      </c>
-      <c r="AC32">
-        <v>0</v>
-      </c>
-      <c r="AD32">
-        <v>0</v>
-      </c>
-      <c r="AE32">
-        <v>0</v>
-      </c>
-      <c r="AF32">
-        <v>0</v>
-      </c>
-      <c r="AG32">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ32">
-        <v>0</v>
-      </c>
-      <c r="AK32">
-        <v>0</v>
-      </c>
-      <c r="AL32">
-        <v>0</v>
-      </c>
-      <c r="AM32">
-        <v>-1</v>
-      </c>
-      <c r="AN32">
-        <v>-1</v>
-      </c>
-      <c r="AO32">
-        <v>-1</v>
-      </c>
-      <c r="AP32">
-        <v>-1</v>
-      </c>
-      <c r="AQ32">
-        <v>0</v>
-      </c>
-      <c r="AR32">
-        <v>0</v>
-      </c>
-      <c r="AS32">
-        <v>0</v>
-      </c>
-      <c r="AT32">
-        <v>0</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>2026-10-15 17:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ethiopia Ethiopia Premier League</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Welwalo Adigrat Uni</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Fasil Ketema</t>
-        </is>
-      </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
-      <c r="H33">
-        <v>0</v>
-      </c>
-      <c r="I33">
-        <v>0</v>
-      </c>
-      <c r="J33">
-        <v>0</v>
-      </c>
-      <c r="K33">
-        <v>0</v>
-      </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>suspended</t>
-        </is>
-      </c>
-      <c r="N33">
-        <v>0</v>
-      </c>
-      <c r="O33">
-        <v>0</v>
-      </c>
-      <c r="P33">
-        <v>0</v>
-      </c>
-      <c r="Q33">
-        <v>0</v>
-      </c>
-      <c r="R33">
-        <v>0</v>
-      </c>
-      <c r="S33">
-        <v>0</v>
-      </c>
-      <c r="T33">
-        <v>0</v>
-      </c>
-      <c r="U33">
-        <v>0</v>
-      </c>
-      <c r="V33">
-        <v>0</v>
-      </c>
-      <c r="W33">
-        <v>0</v>
-      </c>
-      <c r="X33">
-        <v>0</v>
-      </c>
-      <c r="Y33">
-        <v>0</v>
-      </c>
-      <c r="Z33">
-        <v>0</v>
-      </c>
-      <c r="AA33">
-        <v>0</v>
-      </c>
-      <c r="AB33">
-        <v>0</v>
-      </c>
-      <c r="AC33">
-        <v>0</v>
-      </c>
-      <c r="AD33">
-        <v>0</v>
-      </c>
-      <c r="AE33">
-        <v>0</v>
-      </c>
-      <c r="AF33">
-        <v>0</v>
-      </c>
-      <c r="AG33">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ33">
-        <v>0</v>
-      </c>
-      <c r="AK33">
-        <v>0</v>
-      </c>
-      <c r="AL33">
-        <v>0</v>
-      </c>
-      <c r="AM33">
-        <v>-1</v>
-      </c>
-      <c r="AN33">
-        <v>-1</v>
-      </c>
-      <c r="AO33">
-        <v>-1</v>
-      </c>
-      <c r="AP33">
-        <v>-1</v>
-      </c>
-      <c r="AQ33">
-        <v>0</v>
-      </c>
-      <c r="AR33">
-        <v>0</v>
-      </c>
-      <c r="AS33">
-        <v>0</v>
-      </c>
-      <c r="AT33">
-        <v>0</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>2026-10-15 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ethiopia Ethiopia Premier League</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Gamo Chencha</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Sidama Bunna</t>
-        </is>
-      </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
-      <c r="H34">
-        <v>0</v>
-      </c>
-      <c r="I34">
-        <v>0</v>
-      </c>
-      <c r="J34">
-        <v>0</v>
-      </c>
-      <c r="K34">
-        <v>0</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>suspended</t>
-        </is>
-      </c>
-      <c r="N34">
-        <v>0</v>
-      </c>
-      <c r="O34">
-        <v>0</v>
-      </c>
-      <c r="P34">
-        <v>0</v>
-      </c>
-      <c r="Q34">
-        <v>0</v>
-      </c>
-      <c r="R34">
-        <v>0</v>
-      </c>
-      <c r="S34">
-        <v>0</v>
-      </c>
-      <c r="T34">
-        <v>0</v>
-      </c>
-      <c r="U34">
-        <v>0</v>
-      </c>
-      <c r="V34">
-        <v>0</v>
-      </c>
-      <c r="W34">
-        <v>0</v>
-      </c>
-      <c r="X34">
-        <v>0</v>
-      </c>
-      <c r="Y34">
-        <v>0</v>
-      </c>
-      <c r="Z34">
-        <v>0</v>
-      </c>
-      <c r="AA34">
-        <v>0</v>
-      </c>
-      <c r="AB34">
-        <v>0</v>
-      </c>
-      <c r="AC34">
-        <v>0</v>
-      </c>
-      <c r="AD34">
-        <v>0</v>
-      </c>
-      <c r="AE34">
-        <v>0</v>
-      </c>
-      <c r="AF34">
-        <v>0</v>
-      </c>
-      <c r="AG34">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ34">
-        <v>0</v>
-      </c>
-      <c r="AK34">
-        <v>0</v>
-      </c>
-      <c r="AL34">
-        <v>0</v>
-      </c>
-      <c r="AM34">
-        <v>-1</v>
-      </c>
-      <c r="AN34">
-        <v>-1</v>
-      </c>
-      <c r="AO34">
-        <v>-1</v>
-      </c>
-      <c r="AP34">
-        <v>-1</v>
-      </c>
-      <c r="AQ34">
-        <v>0</v>
-      </c>
-      <c r="AR34">
-        <v>0</v>
-      </c>
-      <c r="AS34">
-        <v>0</v>
-      </c>
-      <c r="AT34">
-        <v>0</v>
-      </c>
-      <c r="AU34" t="inlineStr">
         <is>
           <t>2026-10-15 21:00:00</t>
         </is>

--- a/jogos_2026-10-15.xlsx
+++ b/jogos_2026-10-15.xlsx
@@ -1296,55 +1296,55 @@
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2274,55 +2274,55 @@
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2437,55 +2437,55 @@
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL14">
         <v>0</v>

--- a/jogos_2026-10-15.xlsx
+++ b/jogos_2026-10-15.xlsx
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2926,55 +2926,55 @@
         <v>2.55</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Gamo Chencha</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Gamo Chencha</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G19">

--- a/jogos_2026-10-15.xlsx
+++ b/jogos_2026-10-15.xlsx
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Muğlaspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G12">
@@ -2274,55 +2274,55 @@
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>4.68</v>
+        <v>3.6</v>
       </c>
       <c r="R12">
-        <v>2.11</v>
+        <v>2.33</v>
       </c>
       <c r="S12">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T12">
-        <v>2.76</v>
+        <v>3.25</v>
       </c>
       <c r="U12">
-        <v>2.76</v>
+        <v>2.45</v>
       </c>
       <c r="V12">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W12">
+        <v>1.11</v>
+      </c>
+      <c r="X12">
         <v>1.03</v>
       </c>
-      <c r="X12">
-        <v>1.01</v>
-      </c>
       <c r="Y12">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z12">
-        <v>3.28</v>
+        <v>4.04</v>
       </c>
       <c r="AA12">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="AB12">
-        <v>1.79</v>
+        <v>2.06</v>
       </c>
       <c r="AC12">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="AD12">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="AE12">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF12">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AG12">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.21</v>
       </c>
       <c r="AK12">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Muğlaspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="G13">
@@ -2437,55 +2437,55 @@
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>3.6</v>
+        <v>4.68</v>
       </c>
       <c r="R13">
-        <v>2.33</v>
+        <v>2.11</v>
       </c>
       <c r="S13">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T13">
-        <v>3.25</v>
+        <v>2.76</v>
       </c>
       <c r="U13">
-        <v>2.45</v>
+        <v>2.76</v>
       </c>
       <c r="V13">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W13">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z13">
-        <v>4.04</v>
+        <v>3.28</v>
       </c>
       <c r="AA13">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="AB13">
-        <v>2.06</v>
+        <v>1.79</v>
       </c>
       <c r="AC13">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="AD13">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="AE13">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF13">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AG13">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>1.21</v>
       </c>
       <c r="AK13">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Gamo Chencha</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Gamo Chencha</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G19">

--- a/jogos_2026-10-15.xlsx
+++ b/jogos_2026-10-15.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.69</v>
+        <v>2.55</v>
       </c>
       <c r="O9">
-        <v>3.57</v>
+        <v>3.47</v>
       </c>
       <c r="P9">
         <v>2.38</v>
@@ -1803,7 +1803,7 @@
         <v>1.5</v>
       </c>
       <c r="W9">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X9">
         <v>1.02</v>
@@ -1830,10 +1830,10 @@
         <v>1.12</v>
       </c>
       <c r="AF9">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG9">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>

--- a/jogos_2026-10-15.xlsx
+++ b/jogos_2026-10-15.xlsx
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="N10">
-        <v>4.81</v>
+        <v>4.8</v>
       </c>
       <c r="O10">
         <v>4.3</v>

--- a/jogos_2026-10-15.xlsx
+++ b/jogos_2026-10-15.xlsx
@@ -641,7 +641,7 @@
         <v>3.6</v>
       </c>
       <c r="P2">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -1296,55 +1296,55 @@
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>2.97</v>
+        <v>2.8</v>
       </c>
       <c r="R6">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="S6">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T6">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="U6">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="V6">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W6">
         <v>1.08</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z6">
-        <v>3.14</v>
+        <v>3.43</v>
       </c>
       <c r="AA6">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AB6">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AC6">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD6">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AE6">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF6">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG6">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK6">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="O7">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="P7">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1815,10 +1815,10 @@
         <v>4.05</v>
       </c>
       <c r="AA9">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB9">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AC9">
         <v>2.56</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.94</v>
+        <v>2.55</v>
       </c>
       <c r="O11">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P11">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="Q11">
-        <v>3.57</v>
+        <v>3.16</v>
       </c>
       <c r="R11">
-        <v>2.01</v>
+        <v>2.12</v>
       </c>
       <c r="S11">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="T11">
-        <v>2.59</v>
+        <v>2.95</v>
       </c>
       <c r="U11">
-        <v>3.12</v>
+        <v>2.55</v>
       </c>
       <c r="V11">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X11">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y11">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="Z11">
-        <v>2.92</v>
+        <v>3.65</v>
       </c>
       <c r="AA11">
-        <v>2.03</v>
+        <v>1.81</v>
       </c>
       <c r="AB11">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="AC11">
-        <v>3.42</v>
+        <v>2.97</v>
       </c>
       <c r="AD11">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE11">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AF11">
-        <v>1.78</v>
+        <v>1.64</v>
       </c>
       <c r="AG11">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>1.55</v>
       </c>
       <c r="AK11">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q12">
         <v>3.6</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.21</v>
+        <v>1.7</v>
       </c>
       <c r="AK12">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,61 +2428,61 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q13">
-        <v>4.68</v>
+        <v>4.5</v>
       </c>
       <c r="R13">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="S13">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T13">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="U13">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="V13">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W13">
+        <v>1.08</v>
+      </c>
+      <c r="X13">
         <v>1.03</v>
       </c>
-      <c r="X13">
-        <v>1.01</v>
-      </c>
       <c r="Y13">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z13">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="AA13">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB13">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="AC13">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD13">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AE13">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF13">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG13">
         <v>1.91</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK13">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.08</v>
+        <v>2.85</v>
       </c>
       <c r="O14">
         <v>3.74</v>
@@ -2618,7 +2618,7 @@
         <v>1.57</v>
       </c>
       <c r="W14">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X14">
         <v>1.02</v>
@@ -2639,7 +2639,7 @@
         <v>2.38</v>
       </c>
       <c r="AD14">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AE14">
         <v>1.15</v>
@@ -2917,34 +2917,34 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.46</v>
+        <v>2.25</v>
       </c>
       <c r="O16">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="P16">
-        <v>2.55</v>
+        <v>2.93</v>
       </c>
       <c r="Q16">
-        <v>2.83</v>
+        <v>2.59</v>
       </c>
       <c r="R16">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="S16">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T16">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U16">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="V16">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W16">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X16">
         <v>1.02</v>
@@ -2956,16 +2956,16 @@
         <v>3.74</v>
       </c>
       <c r="AA16">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB16">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="AC16">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="AD16">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE16">
         <v>1.1</v>
@@ -2974,7 +2974,7 @@
         <v>1.6</v>
       </c>
       <c r="AG16">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK16">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AL16">
         <v>0</v>

--- a/jogos_2026-10-15.xlsx
+++ b/jogos_2026-10-15.xlsx
@@ -1296,10 +1296,10 @@
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="R6">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="S6">
         <v>1.35</v>
@@ -1320,16 +1320,16 @@
         <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z6">
-        <v>3.43</v>
+        <v>3.46</v>
       </c>
       <c r="AA6">
         <v>1.93</v>
       </c>
       <c r="AB6">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AC6">
         <v>3.3</v>
@@ -1341,10 +1341,10 @@
         <v>1.11</v>
       </c>
       <c r="AF6">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG6">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>1.3</v>
       </c>
       <c r="AK6">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -2117,7 +2117,7 @@
         <v>2.12</v>
       </c>
       <c r="S11">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T11">
         <v>2.95</v>
@@ -2138,13 +2138,13 @@
         <v>1.23</v>
       </c>
       <c r="Z11">
-        <v>3.65</v>
+        <v>3.57</v>
       </c>
       <c r="AA11">
         <v>1.81</v>
       </c>
       <c r="AB11">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AC11">
         <v>2.97</v>
@@ -2153,7 +2153,7 @@
         <v>1.3</v>
       </c>
       <c r="AE11">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF11">
         <v>1.64</v>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="N12">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O12">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P12">
         <v>2.05</v>
@@ -2434,7 +2434,7 @@
         <v>3.4</v>
       </c>
       <c r="P13">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Q13">
         <v>4.5</v>
@@ -2766,16 +2766,16 @@
         <v>2.68</v>
       </c>
       <c r="R15">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="S15">
         <v>1.3</v>
       </c>
       <c r="T15">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="U15">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="V15">
         <v>1.45</v>
@@ -2784,7 +2784,7 @@
         <v>1.11</v>
       </c>
       <c r="X15">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y15">
         <v>1.19</v>

--- a/jogos_2026-10-15.xlsx
+++ b/jogos_2026-10-15.xlsx
@@ -1459,16 +1459,16 @@
         <v>3.38</v>
       </c>
       <c r="Q7">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="R7">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S7">
         <v>1.36</v>
       </c>
       <c r="T7">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="U7">
         <v>2.75</v>
@@ -1477,7 +1477,7 @@
         <v>1.36</v>
       </c>
       <c r="W7">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X7">
         <v>1.01</v>
@@ -1492,7 +1492,7 @@
         <v>1.98</v>
       </c>
       <c r="AB7">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC7">
         <v>3.34</v>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK7">
         <v>1.68</v>
@@ -1776,22 +1776,22 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="O9">
-        <v>3.47</v>
+        <v>3.65</v>
       </c>
       <c r="P9">
         <v>2.38</v>
       </c>
       <c r="Q9">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R9">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S9">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T9">
         <v>3.24</v>
@@ -1803,10 +1803,10 @@
         <v>1.5</v>
       </c>
       <c r="W9">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X9">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y9">
         <v>1.17</v>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK9">
         <v>1.44</v>
@@ -2621,7 +2621,7 @@
         <v>1.14</v>
       </c>
       <c r="X14">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
         <v>1.13</v>
@@ -2633,7 +2633,7 @@
         <v>1.58</v>
       </c>
       <c r="AB14">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AC14">
         <v>2.38</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL14">
         <v>0</v>

--- a/jogos_2026-10-15.xlsx
+++ b/jogos_2026-10-15.xlsx
@@ -1296,7 +1296,7 @@
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="R6">
         <v>2.11</v>
@@ -1305,7 +1305,7 @@
         <v>1.35</v>
       </c>
       <c r="T6">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U6">
         <v>2.7</v>
@@ -1317,7 +1317,7 @@
         <v>1.08</v>
       </c>
       <c r="X6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
         <v>1.28</v>
@@ -1332,7 +1332,7 @@
         <v>1.81</v>
       </c>
       <c r="AC6">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="AD6">
         <v>1.31</v>
@@ -1486,7 +1486,7 @@
         <v>1.28</v>
       </c>
       <c r="Z7">
-        <v>3.08</v>
+        <v>3.31</v>
       </c>
       <c r="AA7">
         <v>1.98</v>
@@ -1495,13 +1495,13 @@
         <v>1.75</v>
       </c>
       <c r="AC7">
-        <v>3.34</v>
+        <v>3.37</v>
       </c>
       <c r="AD7">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AE7">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF7">
         <v>1.77</v>
@@ -1797,7 +1797,7 @@
         <v>3.24</v>
       </c>
       <c r="U9">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="V9">
         <v>1.5</v>
@@ -1806,7 +1806,7 @@
         <v>1.08</v>
       </c>
       <c r="X9">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
         <v>1.17</v>
@@ -1821,19 +1821,19 @@
         <v>2.1</v>
       </c>
       <c r="AC9">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="AD9">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AE9">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF9">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG9">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="N12">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O12">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P12">
         <v>2.05</v>
@@ -2277,13 +2277,13 @@
         <v>3.6</v>
       </c>
       <c r="R12">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="S12">
         <v>1.3</v>
       </c>
       <c r="T12">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="U12">
         <v>2.45</v>
@@ -2307,7 +2307,7 @@
         <v>1.68</v>
       </c>
       <c r="AB12">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="AC12">
         <v>2.7</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.7</v>
+        <v>1.21</v>
       </c>
       <c r="AK12">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2437,25 +2437,25 @@
         <v>1.75</v>
       </c>
       <c r="Q13">
-        <v>4.5</v>
+        <v>4.89</v>
       </c>
       <c r="R13">
         <v>2.2</v>
       </c>
       <c r="S13">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T13">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="U13">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="V13">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W13">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X13">
         <v>1.03</v>
@@ -2467,19 +2467,19 @@
         <v>3.3</v>
       </c>
       <c r="AA13">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AB13">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AC13">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD13">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AE13">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF13">
         <v>1.8</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK13">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.85</v>
+        <v>2.73</v>
       </c>
       <c r="O14">
         <v>3.74</v>
@@ -2615,7 +2615,7 @@
         <v>2.3</v>
       </c>
       <c r="V14">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W14">
         <v>1.14</v>
@@ -2624,13 +2624,13 @@
         <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z14">
         <v>4.6</v>
       </c>
       <c r="AA14">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AB14">
         <v>2.25</v>
@@ -2642,13 +2642,13 @@
         <v>1.53</v>
       </c>
       <c r="AE14">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF14">
         <v>1.5</v>
       </c>
       <c r="AG14">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="O16">
         <v>3.52</v>
@@ -2947,7 +2947,7 @@
         <v>1.08</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y16">
         <v>1.19</v>
@@ -2956,13 +2956,13 @@
         <v>3.74</v>
       </c>
       <c r="AA16">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB16">
         <v>1.98</v>
       </c>
       <c r="AC16">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="AD16">
         <v>1.4</v>

--- a/jogos_2026-10-15.xlsx
+++ b/jogos_2026-10-15.xlsx
@@ -1302,19 +1302,19 @@
         <v>2.11</v>
       </c>
       <c r="S6">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="T6">
         <v>3</v>
       </c>
       <c r="U6">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="V6">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W6">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X6">
         <v>1.01</v>
@@ -1341,10 +1341,10 @@
         <v>1.11</v>
       </c>
       <c r="AF6">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG6">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>1.64</v>
       </c>
       <c r="AG11">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2458,13 +2458,13 @@
         <v>1.03</v>
       </c>
       <c r="X13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z13">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="AA13">
         <v>1.88</v>
@@ -2482,10 +2482,10 @@
         <v>1.05</v>
       </c>
       <c r="AF13">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG13">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="O16">
-        <v>3.52</v>
+        <v>3.7</v>
       </c>
       <c r="P16">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="Q16">
         <v>2.59</v>

--- a/jogos_2026-10-15.xlsx
+++ b/jogos_2026-10-15.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="O2">
         <v>3.6</v>
       </c>
       <c r="P2">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -674,10 +674,10 @@
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="O5">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="P5">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1302,10 +1302,10 @@
         <v>2.11</v>
       </c>
       <c r="S6">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T6">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U6">
         <v>2.86</v>
@@ -1323,13 +1323,13 @@
         <v>1.28</v>
       </c>
       <c r="Z6">
-        <v>3.46</v>
+        <v>3.3</v>
       </c>
       <c r="AA6">
         <v>1.93</v>
       </c>
       <c r="AB6">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AC6">
         <v>3.08</v>
@@ -1341,7 +1341,7 @@
         <v>1.11</v>
       </c>
       <c r="AF6">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG6">
         <v>2</v>
@@ -1453,7 +1453,7 @@
         <v>2.08</v>
       </c>
       <c r="O7">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P7">
         <v>3.38</v>
@@ -1782,7 +1782,7 @@
         <v>3.65</v>
       </c>
       <c r="P9">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="Q9">
         <v>3.25</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="O10">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="P10">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2301,19 +2301,19 @@
         <v>1.22</v>
       </c>
       <c r="Z12">
-        <v>4.04</v>
+        <v>4</v>
       </c>
       <c r="AA12">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AB12">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AC12">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AD12">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AE12">
         <v>1.1</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O13">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P13">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="Q13">
-        <v>4.89</v>
+        <v>5.27</v>
       </c>
       <c r="R13">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S13">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T13">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="U13">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="V13">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W13">
+        <v>1.08</v>
+      </c>
+      <c r="X13">
         <v>1.03</v>
-      </c>
-      <c r="X13">
-        <v>1.01</v>
       </c>
       <c r="Y13">
         <v>1.25</v>
       </c>
       <c r="Z13">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="AA13">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AB13">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AC13">
         <v>3.2</v>
       </c>
       <c r="AD13">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE13">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF13">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AG13">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK13">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2615,7 +2615,7 @@
         <v>2.3</v>
       </c>
       <c r="V14">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W14">
         <v>1.14</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK14">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2766,7 +2766,7 @@
         <v>2.68</v>
       </c>
       <c r="R15">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="S15">
         <v>1.3</v>
@@ -2781,7 +2781,7 @@
         <v>1.45</v>
       </c>
       <c r="W15">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X15">
         <v>1.03</v>
@@ -2793,10 +2793,10 @@
         <v>3.75</v>
       </c>
       <c r="AA15">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AB15">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AC15">
         <v>2.83</v>
@@ -2811,7 +2811,7 @@
         <v>1.62</v>
       </c>
       <c r="AG15">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2923,7 +2923,7 @@
         <v>3.7</v>
       </c>
       <c r="P16">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Q16">
         <v>2.59</v>
@@ -2947,7 +2947,7 @@
         <v>1.08</v>
       </c>
       <c r="X16">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
         <v>1.19</v>
@@ -2959,7 +2959,7 @@
         <v>1.75</v>
       </c>
       <c r="AB16">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC16">
         <v>2.74</v>

--- a/jogos_2026-10-15.xlsx
+++ b/jogos_2026-10-15.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="O2">
-        <v>3.6</v>
+        <v>3.16</v>
       </c>
       <c r="P2">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -1127,10 +1127,10 @@
         <v>1.25</v>
       </c>
       <c r="O5">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="P5">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="Q5">
         <v>1.53</v>
@@ -1299,7 +1299,7 @@
         <v>2.6</v>
       </c>
       <c r="R6">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="S6">
         <v>1.4</v>
@@ -1326,10 +1326,10 @@
         <v>3.3</v>
       </c>
       <c r="AA6">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB6">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AC6">
         <v>3.08</v>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AK6">
         <v>1.64</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="O7">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="P7">
-        <v>3.38</v>
+        <v>3.12</v>
       </c>
       <c r="Q7">
         <v>2.63</v>
@@ -1489,7 +1489,7 @@
         <v>3.31</v>
       </c>
       <c r="AA7">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AB7">
         <v>1.75</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="O9">
         <v>3.65</v>
       </c>
       <c r="P9">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="Q9">
         <v>3.25</v>
@@ -1939,31 +1939,31 @@
         </is>
       </c>
       <c r="N10">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="O10">
         <v>4.2</v>
       </c>
       <c r="P10">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Q10">
+        <v>4.45</v>
+      </c>
+      <c r="R10">
+        <v>2.7</v>
+      </c>
+      <c r="S10">
+        <v>1.18</v>
+      </c>
+      <c r="T10">
         <v>4.5</v>
       </c>
-      <c r="R10">
-        <v>2.63</v>
-      </c>
-      <c r="S10">
-        <v>1.2</v>
-      </c>
-      <c r="T10">
-        <v>4</v>
-      </c>
       <c r="U10">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="V10">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="W10">
         <v>1.17</v>
@@ -1972,31 +1972,31 @@
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z10">
-        <v>5.45</v>
+        <v>5.75</v>
       </c>
       <c r="AA10">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AB10">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="AC10">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AD10">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="AE10">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AF10">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AG10">
-        <v>2.48</v>
+        <v>2.57</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>1.14</v>
       </c>
       <c r="AK10">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AK11">
         <v>1.4</v>
@@ -2304,7 +2304,7 @@
         <v>4</v>
       </c>
       <c r="AA12">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AB12">
         <v>1.99</v>
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="N13">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O13">
         <v>3.6</v>
       </c>
       <c r="P13">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Q13">
         <v>5.27</v>
       </c>
       <c r="R13">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="S13">
         <v>1.33</v>
@@ -2470,7 +2470,7 @@
         <v>1.83</v>
       </c>
       <c r="AB13">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AC13">
         <v>3.2</v>
@@ -2485,7 +2485,7 @@
         <v>1.81</v>
       </c>
       <c r="AG13">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.73</v>
+        <v>2.97</v>
       </c>
       <c r="O14">
-        <v>3.74</v>
+        <v>3.37</v>
       </c>
       <c r="P14">
-        <v>2.09</v>
+        <v>1.96</v>
       </c>
       <c r="Q14">
         <v>3.48</v>

--- a/jogos_2026-10-15.xlsx
+++ b/jogos_2026-10-15.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="O2">
         <v>3.16</v>
       </c>
       <c r="P2">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -1450,16 +1450,16 @@
         </is>
       </c>
       <c r="N7">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="O7">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="P7">
-        <v>3.12</v>
+        <v>3.38</v>
       </c>
       <c r="Q7">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="R7">
         <v>2.1</v>
@@ -1492,7 +1492,7 @@
         <v>2</v>
       </c>
       <c r="AB7">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC7">
         <v>3.37</v>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK7">
         <v>1.68</v>
@@ -1797,7 +1797,7 @@
         <v>3.24</v>
       </c>
       <c r="U9">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="V9">
         <v>1.5</v>
@@ -1815,10 +1815,10 @@
         <v>4.05</v>
       </c>
       <c r="AA9">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB9">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC9">
         <v>2.63</v>
@@ -1849,7 +1849,7 @@
         <v>1.25</v>
       </c>
       <c r="AK9">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2591,19 +2591,19 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.97</v>
+        <v>2.75</v>
       </c>
       <c r="O14">
-        <v>3.37</v>
+        <v>3.74</v>
       </c>
       <c r="P14">
-        <v>1.96</v>
+        <v>2.09</v>
       </c>
       <c r="Q14">
-        <v>3.48</v>
+        <v>3.55</v>
       </c>
       <c r="R14">
-        <v>2.28</v>
+        <v>2.43</v>
       </c>
       <c r="S14">
         <v>1.24</v>
@@ -2615,7 +2615,7 @@
         <v>2.3</v>
       </c>
       <c r="V14">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W14">
         <v>1.14</v>
@@ -2633,7 +2633,7 @@
         <v>1.57</v>
       </c>
       <c r="AB14">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AC14">
         <v>2.38</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK14">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AL14">
         <v>0</v>

--- a/jogos_2026-10-15.xlsx
+++ b/jogos_2026-10-15.xlsx
@@ -1954,7 +1954,7 @@
         <v>2.7</v>
       </c>
       <c r="S10">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T10">
         <v>4.5</v>
@@ -1963,13 +1963,13 @@
         <v>2</v>
       </c>
       <c r="V10">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W10">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y10">
         <v>1.07</v>
@@ -1978,10 +1978,10 @@
         <v>5.75</v>
       </c>
       <c r="AA10">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AB10">
-        <v>2.78</v>
+        <v>3.25</v>
       </c>
       <c r="AC10">
         <v>1.9</v>
@@ -1990,7 +1990,7 @@
         <v>1.77</v>
       </c>
       <c r="AE10">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AF10">
         <v>1.42</v>
@@ -2012,7 +2012,7 @@
         <v>1.14</v>
       </c>
       <c r="AK10">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>1.3</v>
       </c>
       <c r="T12">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="U12">
         <v>2.45</v>
@@ -2434,13 +2434,13 @@
         <v>3.6</v>
       </c>
       <c r="P13">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Q13">
-        <v>5.27</v>
+        <v>5.37</v>
       </c>
       <c r="R13">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="S13">
         <v>1.33</v>
@@ -2449,10 +2449,10 @@
         <v>3</v>
       </c>
       <c r="U13">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="V13">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W13">
         <v>1.08</v>
@@ -2467,10 +2467,10 @@
         <v>3.6</v>
       </c>
       <c r="AA13">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AB13">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AC13">
         <v>3.2</v>
@@ -2482,10 +2482,10 @@
         <v>1.11</v>
       </c>
       <c r="AF13">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AG13">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK13">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2932,7 +2932,7 @@
         <v>2.16</v>
       </c>
       <c r="S16">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T16">
         <v>2.9</v>
@@ -2947,19 +2947,19 @@
         <v>1.08</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z16">
-        <v>3.74</v>
+        <v>4.2</v>
       </c>
       <c r="AA16">
         <v>1.75</v>
       </c>
       <c r="AB16">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC16">
         <v>2.74</v>

--- a/jogos_2026-10-15.xlsx
+++ b/jogos_2026-10-15.xlsx
@@ -1489,7 +1489,7 @@
         <v>3.31</v>
       </c>
       <c r="AA7">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB7">
         <v>1.8</v>
@@ -1978,10 +1978,10 @@
         <v>5.75</v>
       </c>
       <c r="AA10">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AB10">
-        <v>3.25</v>
+        <v>2.78</v>
       </c>
       <c r="AC10">
         <v>1.9</v>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="N12">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="O12">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P12">
         <v>2.05</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.21</v>
+        <v>1.63</v>
       </c>
       <c r="AK12">
         <v>1.26</v>
@@ -2434,7 +2434,7 @@
         <v>3.6</v>
       </c>
       <c r="P13">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="Q13">
         <v>5.37</v>
@@ -2467,10 +2467,10 @@
         <v>3.6</v>
       </c>
       <c r="AA13">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AB13">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AC13">
         <v>3.2</v>
@@ -2485,7 +2485,7 @@
         <v>1.82</v>
       </c>
       <c r="AG13">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>1.18</v>
       </c>
       <c r="AK13">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AL13">
         <v>0</v>

--- a/jogos_2026-10-15.xlsx
+++ b/jogos_2026-10-15.xlsx
@@ -1296,22 +1296,22 @@
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="R6">
         <v>2.08</v>
       </c>
       <c r="S6">
+        <v>1.35</v>
+      </c>
+      <c r="T6">
+        <v>3</v>
+      </c>
+      <c r="U6">
+        <v>2.6</v>
+      </c>
+      <c r="V6">
         <v>1.4</v>
-      </c>
-      <c r="T6">
-        <v>2.88</v>
-      </c>
-      <c r="U6">
-        <v>2.86</v>
-      </c>
-      <c r="V6">
-        <v>1.39</v>
       </c>
       <c r="W6">
         <v>1.06</v>
@@ -1323,7 +1323,7 @@
         <v>1.28</v>
       </c>
       <c r="Z6">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA6">
         <v>1.9</v>
@@ -1335,13 +1335,13 @@
         <v>3.08</v>
       </c>
       <c r="AD6">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE6">
         <v>1.11</v>
       </c>
       <c r="AF6">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG6">
         <v>2</v>
@@ -1453,7 +1453,7 @@
         <v>2.08</v>
       </c>
       <c r="O7">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P7">
         <v>3.38</v>
@@ -2301,19 +2301,19 @@
         <v>1.22</v>
       </c>
       <c r="Z12">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA12">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AB12">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="AC12">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AD12">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE12">
         <v>1.1</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.63</v>
+        <v>1.21</v>
       </c>
       <c r="AK12">
         <v>1.26</v>
@@ -2434,7 +2434,7 @@
         <v>3.6</v>
       </c>
       <c r="P13">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="Q13">
         <v>5.37</v>
@@ -2467,7 +2467,7 @@
         <v>3.6</v>
       </c>
       <c r="AA13">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AB13">
         <v>1.88</v>
@@ -2485,7 +2485,7 @@
         <v>1.82</v>
       </c>
       <c r="AG13">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>

--- a/jogos_2026-10-15.xlsx
+++ b/jogos_2026-10-15.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="O2">
         <v>3.16</v>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="O7">
         <v>3.4</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="O14">
         <v>3.74</v>
       </c>
       <c r="P14">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="Q14">
         <v>3.55</v>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="AK14">
         <v>1.26</v>

--- a/jogos_2026-10-15.xlsx
+++ b/jogos_2026-10-15.xlsx
@@ -1302,13 +1302,13 @@
         <v>2.08</v>
       </c>
       <c r="S6">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="T6">
         <v>3</v>
       </c>
       <c r="U6">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="V6">
         <v>1.4</v>
@@ -1341,10 +1341,10 @@
         <v>1.11</v>
       </c>
       <c r="AF6">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG6">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>3.35</v>
       </c>
       <c r="P12">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="Q12">
         <v>3.6</v>

--- a/jogos_2026-10-15.xlsx
+++ b/jogos_2026-10-15.xlsx
@@ -638,7 +638,7 @@
         <v>3.1</v>
       </c>
       <c r="O2">
-        <v>3.16</v>
+        <v>3.5</v>
       </c>
       <c r="P2">
         <v>2.06</v>
@@ -1124,31 +1124,31 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="O5">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="P5">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="Q5">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="R5">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="S5">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="T5">
-        <v>4.15</v>
+        <v>3.98</v>
       </c>
       <c r="U5">
         <v>2</v>
       </c>
       <c r="V5">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="W5">
         <v>1.2</v>
@@ -1160,28 +1160,28 @@
         <v>1.08</v>
       </c>
       <c r="Z5">
-        <v>5.65</v>
+        <v>5.6</v>
       </c>
       <c r="AA5">
         <v>1.35</v>
       </c>
       <c r="AB5">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="AC5">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AD5">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AE5">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AF5">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AG5">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>1.03</v>
       </c>
       <c r="AK5">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="O7">
         <v>3.4</v>
@@ -1486,16 +1486,16 @@
         <v>1.28</v>
       </c>
       <c r="Z7">
-        <v>3.31</v>
+        <v>3.34</v>
       </c>
       <c r="AA7">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AB7">
         <v>1.8</v>
       </c>
       <c r="AC7">
-        <v>3.37</v>
+        <v>3.34</v>
       </c>
       <c r="AD7">
         <v>1.3</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="O9">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P9">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="Q9">
         <v>3.25</v>
@@ -1809,31 +1809,31 @@
         <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z9">
-        <v>4.05</v>
+        <v>4.26</v>
       </c>
       <c r="AA9">
         <v>1.67</v>
       </c>
       <c r="AB9">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AC9">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="AD9">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AE9">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AF9">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG9">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="O10">
         <v>4.2</v>
       </c>
       <c r="P10">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="Q10">
         <v>4.45</v>
@@ -1954,7 +1954,7 @@
         <v>2.7</v>
       </c>
       <c r="S10">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T10">
         <v>4.5</v>
@@ -1966,7 +1966,7 @@
         <v>1.73</v>
       </c>
       <c r="W10">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X10">
         <v>1</v>
@@ -2778,7 +2778,7 @@
         <v>2.45</v>
       </c>
       <c r="V15">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W15">
         <v>1.05</v>
@@ -2827,7 +2827,7 @@
         <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2923,7 +2923,7 @@
         <v>3.7</v>
       </c>
       <c r="P16">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="Q16">
         <v>2.59</v>

--- a/jogos_2026-10-15.xlsx
+++ b/jogos_2026-10-15.xlsx
@@ -638,7 +638,7 @@
         <v>3.1</v>
       </c>
       <c r="O2">
-        <v>3.5</v>
+        <v>3.16</v>
       </c>
       <c r="P2">
         <v>2.06</v>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="O7">
         <v>3.4</v>
@@ -1471,7 +1471,7 @@
         <v>2.88</v>
       </c>
       <c r="U7">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="V7">
         <v>1.36</v>
@@ -1785,13 +1785,13 @@
         <v>2.62</v>
       </c>
       <c r="Q9">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="R9">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S9">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T9">
         <v>3.24</v>
@@ -1800,7 +1800,7 @@
         <v>2.3</v>
       </c>
       <c r="V9">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W9">
         <v>1.08</v>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK9">
         <v>1.35</v>
@@ -2289,10 +2289,10 @@
         <v>2.45</v>
       </c>
       <c r="V12">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W12">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X12">
         <v>1.03</v>
@@ -2935,7 +2935,7 @@
         <v>1.3</v>
       </c>
       <c r="T16">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="U16">
         <v>2.41</v>
@@ -2947,7 +2947,7 @@
         <v>1.08</v>
       </c>
       <c r="X16">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
         <v>1.22</v>

--- a/jogos_2026-10-15.xlsx
+++ b/jogos_2026-10-15.xlsx
@@ -638,7 +638,7 @@
         <v>3.1</v>
       </c>
       <c r="O2">
-        <v>3.16</v>
+        <v>3.07</v>
       </c>
       <c r="P2">
         <v>2.06</v>
@@ -1296,7 +1296,7 @@
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>2.47</v>
+        <v>2.64</v>
       </c>
       <c r="R6">
         <v>2.08</v>
@@ -1308,7 +1308,7 @@
         <v>3</v>
       </c>
       <c r="U6">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="V6">
         <v>1.4</v>
@@ -1320,13 +1320,13 @@
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z6">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA6">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB6">
         <v>1.81</v>
@@ -1335,10 +1335,10 @@
         <v>3.08</v>
       </c>
       <c r="AD6">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE6">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF6">
         <v>1.75</v>
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="N7">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O7">
-        <v>3.4</v>
+        <v>3.46</v>
       </c>
       <c r="P7">
         <v>3.38</v>
@@ -1480,13 +1480,13 @@
         <v>1.06</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y7">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z7">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="AA7">
         <v>1.9</v>
@@ -1495,7 +1495,7 @@
         <v>1.8</v>
       </c>
       <c r="AC7">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="AD7">
         <v>1.3</v>
@@ -1504,10 +1504,10 @@
         <v>1.1</v>
       </c>
       <c r="AF7">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG7">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="O9">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P9">
         <v>2.62</v>
@@ -1809,7 +1809,7 @@
         <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z9">
         <v>4.26</v>
@@ -1849,7 +1849,7 @@
         <v>1.22</v>
       </c>
       <c r="AK9">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,22 +1939,22 @@
         </is>
       </c>
       <c r="N10">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="O10">
         <v>4.2</v>
       </c>
       <c r="P10">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="Q10">
-        <v>4.45</v>
+        <v>5</v>
       </c>
       <c r="R10">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="S10">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T10">
         <v>4.5</v>
@@ -1966,37 +1966,37 @@
         <v>1.73</v>
       </c>
       <c r="W10">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X10">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z10">
-        <v>5.75</v>
+        <v>5.7</v>
       </c>
       <c r="AA10">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AB10">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="AC10">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="AD10">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AE10">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF10">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AG10">
-        <v>2.57</v>
+        <v>2.42</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>1.14</v>
       </c>
       <c r="AK10">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2156,7 +2156,7 @@
         <v>1.11</v>
       </c>
       <c r="AF11">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AG11">
         <v>2.05</v>
@@ -2295,10 +2295,10 @@
         <v>1.08</v>
       </c>
       <c r="X12">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z12">
         <v>4.1</v>
@@ -2627,7 +2627,7 @@
         <v>1.17</v>
       </c>
       <c r="Z14">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AA14">
         <v>1.57</v>
@@ -2636,10 +2636,10 @@
         <v>2.38</v>
       </c>
       <c r="AC14">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AD14">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AE14">
         <v>1.2</v>
@@ -2648,7 +2648,7 @@
         <v>1.5</v>
       </c>
       <c r="AG14">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>

--- a/jogos_2026-10-15.xlsx
+++ b/jogos_2026-10-15.xlsx
@@ -638,10 +638,10 @@
         <v>3.1</v>
       </c>
       <c r="O2">
-        <v>3.07</v>
+        <v>3.16</v>
       </c>
       <c r="P2">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -674,10 +674,10 @@
         <v>0</v>
       </c>
       <c r="AA2">
+        <v>1.95</v>
+      </c>
+      <c r="AB2">
         <v>1.85</v>
-      </c>
-      <c r="AB2">
-        <v>1.95</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O7">
         <v>3.46</v>
@@ -1459,19 +1459,19 @@
         <v>3.38</v>
       </c>
       <c r="Q7">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="R7">
         <v>2.1</v>
       </c>
       <c r="S7">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T7">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U7">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="V7">
         <v>1.36</v>
@@ -1480,34 +1480,34 @@
         <v>1.06</v>
       </c>
       <c r="X7">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z7">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="AA7">
         <v>1.9</v>
       </c>
       <c r="AB7">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AC7">
         <v>3.4</v>
       </c>
       <c r="AD7">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE7">
         <v>1.1</v>
       </c>
       <c r="AF7">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG7">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK7">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC8">
         <v>0</v>
@@ -1815,7 +1815,7 @@
         <v>4.26</v>
       </c>
       <c r="AA9">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB9">
         <v>2.12</v>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK9">
         <v>1.38</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="O10">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P10">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="Q10">
         <v>5</v>
@@ -1954,7 +1954,7 @@
         <v>2.57</v>
       </c>
       <c r="S10">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T10">
         <v>4.5</v>
@@ -1966,7 +1966,7 @@
         <v>1.73</v>
       </c>
       <c r="W10">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X10">
         <v>1.01</v>
@@ -2012,7 +2012,7 @@
         <v>1.14</v>
       </c>
       <c r="AK10">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N18">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N19">

--- a/jogos_2026-10-15.xlsx
+++ b/jogos_2026-10-15.xlsx
@@ -1133,10 +1133,10 @@
         <v>9</v>
       </c>
       <c r="Q5">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="R5">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="S5">
         <v>1.17</v>
@@ -1166,7 +1166,7 @@
         <v>1.35</v>
       </c>
       <c r="AB5">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AC5">
         <v>1.9</v>
@@ -1197,7 +1197,7 @@
         <v>1.03</v>
       </c>
       <c r="AK5">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1323,10 +1323,10 @@
         <v>1.29</v>
       </c>
       <c r="Z6">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA6">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AB6">
         <v>1.81</v>
@@ -1338,7 +1338,7 @@
         <v>1.3</v>
       </c>
       <c r="AE6">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF6">
         <v>1.75</v>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="N7">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O7">
         <v>3.46</v>
@@ -1471,7 +1471,7 @@
         <v>3</v>
       </c>
       <c r="U7">
-        <v>2.76</v>
+        <v>2.62</v>
       </c>
       <c r="V7">
         <v>1.36</v>
@@ -1480,16 +1480,16 @@
         <v>1.06</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
         <v>1.29</v>
       </c>
       <c r="Z7">
-        <v>3.54</v>
+        <v>3.57</v>
       </c>
       <c r="AA7">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AB7">
         <v>1.87</v>
@@ -1498,10 +1498,10 @@
         <v>3.4</v>
       </c>
       <c r="AD7">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE7">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF7">
         <v>1.73</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="O9">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P9">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="Q9">
         <v>3.1</v>
@@ -1797,7 +1797,7 @@
         <v>3.24</v>
       </c>
       <c r="U9">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V9">
         <v>1.45</v>
@@ -1812,7 +1812,7 @@
         <v>1.2</v>
       </c>
       <c r="Z9">
-        <v>4.26</v>
+        <v>4.3</v>
       </c>
       <c r="AA9">
         <v>1.7</v>
@@ -2138,7 +2138,7 @@
         <v>1.23</v>
       </c>
       <c r="Z11">
-        <v>3.57</v>
+        <v>3.6</v>
       </c>
       <c r="AA11">
         <v>1.81</v>
@@ -2153,13 +2153,13 @@
         <v>1.3</v>
       </c>
       <c r="AE11">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF11">
         <v>1.67</v>
       </c>
       <c r="AG11">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>3.35</v>
       </c>
       <c r="P12">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="Q12">
         <v>3.6</v>
@@ -2431,10 +2431,10 @@
         <v>4.4</v>
       </c>
       <c r="O13">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="P13">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Q13">
         <v>5.37</v>
@@ -2479,7 +2479,7 @@
         <v>1.3</v>
       </c>
       <c r="AE13">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF13">
         <v>1.82</v>
@@ -2615,7 +2615,7 @@
         <v>2.3</v>
       </c>
       <c r="V14">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W14">
         <v>1.14</v>
@@ -2630,7 +2630,7 @@
         <v>5</v>
       </c>
       <c r="AA14">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB14">
         <v>2.38</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="O15">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P15">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="Q15">
         <v>2.68</v>
@@ -2784,7 +2784,7 @@
         <v>1.05</v>
       </c>
       <c r="X15">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
         <v>1.19</v>
@@ -2920,10 +2920,10 @@
         <v>2.25</v>
       </c>
       <c r="O16">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P16">
-        <v>2.93</v>
+        <v>2.86</v>
       </c>
       <c r="Q16">
         <v>2.59</v>
@@ -2947,7 +2947,7 @@
         <v>1.08</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
         <v>1.22</v>

--- a/jogos_2026-10-15.xlsx
+++ b/jogos_2026-10-15.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O2">
         <v>3.16</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q6">
         <v>2.64</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.06</v>
+        <v>2.92</v>
       </c>
       <c r="O8">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="P8">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O9">
         <v>3.5</v>
       </c>
       <c r="P9">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
       <c r="Q9">
         <v>3.1</v>
@@ -1815,7 +1815,7 @@
         <v>4.3</v>
       </c>
       <c r="AA9">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB9">
         <v>2.12</v>
@@ -2431,7 +2431,7 @@
         <v>4.4</v>
       </c>
       <c r="O13">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="P13">
         <v>1.65</v>

--- a/jogos_2026-10-15.xlsx
+++ b/jogos_2026-10-15.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="O5">
         <v>6.5</v>
@@ -1133,25 +1133,25 @@
         <v>9</v>
       </c>
       <c r="Q5">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="R5">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="S5">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T5">
-        <v>3.98</v>
+        <v>4.25</v>
       </c>
       <c r="U5">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="V5">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="W5">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X5">
         <v>1.01</v>
@@ -1160,28 +1160,28 @@
         <v>1.08</v>
       </c>
       <c r="Z5">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="AA5">
+        <v>1.31</v>
+      </c>
+      <c r="AB5">
+        <v>3.5</v>
+      </c>
+      <c r="AC5">
+        <v>1.82</v>
+      </c>
+      <c r="AD5">
+        <v>1.85</v>
+      </c>
+      <c r="AE5">
         <v>1.35</v>
       </c>
-      <c r="AB5">
-        <v>3</v>
-      </c>
-      <c r="AC5">
-        <v>1.9</v>
-      </c>
-      <c r="AD5">
-        <v>1.77</v>
-      </c>
-      <c r="AE5">
-        <v>1.31</v>
-      </c>
       <c r="AF5">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG5">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>1.03</v>
       </c>
       <c r="AK5">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="O6">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P6">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Q6">
         <v>2.64</v>
@@ -1305,7 +1305,7 @@
         <v>1.39</v>
       </c>
       <c r="T6">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U6">
         <v>2.62</v>
@@ -1338,13 +1338,13 @@
         <v>1.3</v>
       </c>
       <c r="AE6">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF6">
         <v>1.75</v>
       </c>
       <c r="AG6">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>3.35</v>
       </c>
       <c r="P12">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="Q12">
         <v>3.6</v>
@@ -2440,7 +2440,7 @@
         <v>5.37</v>
       </c>
       <c r="R13">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="S13">
         <v>1.33</v>
@@ -2485,7 +2485,7 @@
         <v>1.82</v>
       </c>
       <c r="AG13">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>1.18</v>
       </c>
       <c r="AK13">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="O15">
         <v>3.4</v>
       </c>
       <c r="P15">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="Q15">
         <v>2.68</v>
@@ -2784,7 +2784,7 @@
         <v>1.05</v>
       </c>
       <c r="X15">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y15">
         <v>1.19</v>

--- a/jogos_2026-10-15.xlsx
+++ b/jogos_2026-10-15.xlsx
@@ -638,7 +638,7 @@
         <v>3.2</v>
       </c>
       <c r="O2">
-        <v>3.16</v>
+        <v>3.5</v>
       </c>
       <c r="P2">
         <v>1.97</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>9</v>
+        <v>7.01</v>
       </c>
       <c r="O3">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="P3">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -982,7 +982,7 @@
         <v>2.69</v>
       </c>
       <c r="U4">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="V4">
         <v>1.36</v>
@@ -1015,10 +1015,10 @@
         <v>1.06</v>
       </c>
       <c r="AF4">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG4">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O7">
-        <v>3.46</v>
+        <v>3.25</v>
       </c>
       <c r="P7">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="Q7">
         <v>2.7</v>
@@ -1471,7 +1471,7 @@
         <v>3</v>
       </c>
       <c r="U7">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="V7">
         <v>1.36</v>
@@ -1483,28 +1483,28 @@
         <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="Z7">
-        <v>3.57</v>
+        <v>3.34</v>
       </c>
       <c r="AA7">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="AB7">
         <v>1.87</v>
       </c>
       <c r="AC7">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="AD7">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AE7">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF7">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG7">
         <v>2.1</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="O8">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P8">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1788,7 +1788,7 @@
         <v>3.1</v>
       </c>
       <c r="R9">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="S9">
         <v>1.25</v>
@@ -1797,13 +1797,13 @@
         <v>3.24</v>
       </c>
       <c r="U9">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="V9">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W9">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X9">
         <v>1.02</v>
@@ -1812,10 +1812,10 @@
         <v>1.2</v>
       </c>
       <c r="Z9">
-        <v>4.3</v>
+        <v>4.31</v>
       </c>
       <c r="AA9">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AB9">
         <v>2.12</v>
@@ -1948,13 +1948,13 @@
         <v>1.48</v>
       </c>
       <c r="Q10">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="R10">
         <v>2.57</v>
       </c>
       <c r="S10">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T10">
         <v>4.5</v>
@@ -1963,7 +1963,7 @@
         <v>2</v>
       </c>
       <c r="V10">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="W10">
         <v>1.17</v>
@@ -1984,10 +1984,10 @@
         <v>3.1</v>
       </c>
       <c r="AC10">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="AD10">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AE10">
         <v>1.33</v>
@@ -2156,10 +2156,10 @@
         <v>1.12</v>
       </c>
       <c r="AF11">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AG11">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2962,13 +2962,13 @@
         <v>2.05</v>
       </c>
       <c r="AC16">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="AD16">
         <v>1.4</v>
       </c>
       <c r="AE16">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF16">
         <v>1.6</v>

--- a/jogos_2026-10-15.xlsx
+++ b/jogos_2026-10-15.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>7.01</v>
+        <v>1.76</v>
       </c>
       <c r="O3">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="P3">
-        <v>1.4</v>
+        <v>4.33</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.76</v>
+        <v>7.01</v>
       </c>
       <c r="O4">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="P4">
-        <v>4.33</v>
+        <v>1.4</v>
       </c>
       <c r="Q4">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y4">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z4">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="AA4">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC4">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK4">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1296,7 +1296,7 @@
         <v>3.2</v>
       </c>
       <c r="Q6">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="R6">
         <v>2.08</v>
@@ -1305,7 +1305,7 @@
         <v>1.39</v>
       </c>
       <c r="T6">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U6">
         <v>2.62</v>
@@ -1320,16 +1320,16 @@
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z6">
         <v>3.3</v>
       </c>
       <c r="AA6">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AB6">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AC6">
         <v>3.08</v>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="O8">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P8">
         <v>2.38</v>
@@ -1782,13 +1782,13 @@
         <v>3.5</v>
       </c>
       <c r="P9">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q9">
         <v>3.1</v>
       </c>
       <c r="R9">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="S9">
         <v>1.25</v>
@@ -1812,7 +1812,7 @@
         <v>1.2</v>
       </c>
       <c r="Z9">
-        <v>4.31</v>
+        <v>4.35</v>
       </c>
       <c r="AA9">
         <v>1.67</v>
@@ -1945,13 +1945,13 @@
         <v>4.33</v>
       </c>
       <c r="P10">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Q10">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="R10">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="S10">
         <v>1.17</v>
@@ -1963,7 +1963,7 @@
         <v>2</v>
       </c>
       <c r="V10">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="W10">
         <v>1.17</v>
@@ -1981,22 +1981,22 @@
         <v>1.35</v>
       </c>
       <c r="AB10">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="AC10">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AD10">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AE10">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF10">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AG10">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>2.12</v>
       </c>
       <c r="S11">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T11">
         <v>2.95</v>
@@ -2138,7 +2138,7 @@
         <v>1.23</v>
       </c>
       <c r="Z11">
-        <v>3.6</v>
+        <v>3.63</v>
       </c>
       <c r="AA11">
         <v>1.81</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="O12">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="P12">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q12">
         <v>3.6</v>
@@ -2316,7 +2316,7 @@
         <v>1.4</v>
       </c>
       <c r="AE12">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AF12">
         <v>1.62</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.21</v>
+        <v>1.7</v>
       </c>
       <c r="AK12">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2467,7 +2467,7 @@
         <v>3.6</v>
       </c>
       <c r="AA13">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AB13">
         <v>1.88</v>
@@ -2501,7 +2501,7 @@
         <v>1.18</v>
       </c>
       <c r="AK13">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AL13">
         <v>0</v>

--- a/jogos_2026-10-15.xlsx
+++ b/jogos_2026-10-15.xlsx
@@ -1453,10 +1453,10 @@
         <v>2.05</v>
       </c>
       <c r="O7">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="P7">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q7">
         <v>2.7</v>
@@ -1619,7 +1619,7 @@
         <v>3.1</v>
       </c>
       <c r="P8">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB8">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AC8">
         <v>0</v>
@@ -1782,10 +1782,10 @@
         <v>3.5</v>
       </c>
       <c r="P9">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="Q9">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="R9">
         <v>2.38</v>
@@ -1797,7 +1797,7 @@
         <v>3.24</v>
       </c>
       <c r="U9">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="V9">
         <v>1.5</v>
@@ -1812,7 +1812,7 @@
         <v>1.2</v>
       </c>
       <c r="Z9">
-        <v>4.35</v>
+        <v>4.36</v>
       </c>
       <c r="AA9">
         <v>1.67</v>
@@ -1821,10 +1821,10 @@
         <v>2.12</v>
       </c>
       <c r="AC9">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="AD9">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE9">
         <v>1.12</v>
@@ -1833,7 +1833,7 @@
         <v>1.53</v>
       </c>
       <c r="AG9">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK9">
         <v>1.38</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N11">
@@ -2138,13 +2138,13 @@
         <v>1.23</v>
       </c>
       <c r="Z11">
-        <v>3.63</v>
+        <v>3.58</v>
       </c>
       <c r="AA11">
         <v>1.81</v>
       </c>
       <c r="AB11">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AC11">
         <v>2.97</v>
@@ -2153,7 +2153,7 @@
         <v>1.3</v>
       </c>
       <c r="AE11">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF11">
         <v>1.64</v>
@@ -2274,7 +2274,7 @@
         <v>1.95</v>
       </c>
       <c r="Q12">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="R12">
         <v>2.19</v>
@@ -2319,7 +2319,7 @@
         <v>1.16</v>
       </c>
       <c r="AF12">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG12">
         <v>2.2</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O13">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P13">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="Q13">
         <v>5.37</v>
@@ -2920,7 +2920,7 @@
         <v>2.25</v>
       </c>
       <c r="O16">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="P16">
         <v>2.86</v>
@@ -2962,7 +2962,7 @@
         <v>2.05</v>
       </c>
       <c r="AC16">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="AD16">
         <v>1.4</v>

--- a/jogos_2026-10-15.xlsx
+++ b/jogos_2026-10-15.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="O3">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P3">
-        <v>4.33</v>
+        <v>3.85</v>
       </c>
       <c r="Q3">
         <v>2.28</v>
@@ -819,13 +819,13 @@
         <v>2.69</v>
       </c>
       <c r="U3">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="V3">
         <v>1.36</v>
       </c>
       <c r="W3">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X3">
         <v>1.02</v>
@@ -852,10 +852,10 @@
         <v>1.06</v>
       </c>
       <c r="AF3">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG3">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>7.01</v>
+        <v>5.46</v>
       </c>
       <c r="O4">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="P4">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,31 +1124,31 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="O5">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="P5">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q5">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="R5">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="S5">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T5">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="U5">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="V5">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="W5">
         <v>1.22</v>
@@ -1157,31 +1157,31 @@
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z5">
-        <v>6.1</v>
+        <v>6.45</v>
       </c>
       <c r="AA5">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AB5">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AC5">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="AD5">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AE5">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AF5">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="AG5">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AK5">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1302,13 +1302,13 @@
         <v>2.08</v>
       </c>
       <c r="S6">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T6">
         <v>3</v>
       </c>
       <c r="U6">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="V6">
         <v>1.4</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="O8">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P8">
-        <v>2.29</v>
+        <v>1.93</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Muğlaspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.73</v>
+        <v>4.6</v>
       </c>
       <c r="O12">
-        <v>3.38</v>
+        <v>3.7</v>
       </c>
       <c r="P12">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="Q12">
-        <v>3.75</v>
+        <v>5.37</v>
       </c>
       <c r="R12">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="S12">
+        <v>1.33</v>
+      </c>
+      <c r="T12">
+        <v>3</v>
+      </c>
+      <c r="U12">
+        <v>2.68</v>
+      </c>
+      <c r="V12">
+        <v>1.37</v>
+      </c>
+      <c r="W12">
+        <v>1.1</v>
+      </c>
+      <c r="X12">
+        <v>1.03</v>
+      </c>
+      <c r="Y12">
+        <v>1.25</v>
+      </c>
+      <c r="Z12">
+        <v>3.6</v>
+      </c>
+      <c r="AA12">
+        <v>1.89</v>
+      </c>
+      <c r="AB12">
+        <v>1.88</v>
+      </c>
+      <c r="AC12">
+        <v>3.2</v>
+      </c>
+      <c r="AD12">
         <v>1.3</v>
       </c>
-      <c r="T12">
-        <v>3.2</v>
-      </c>
-      <c r="U12">
-        <v>2.45</v>
-      </c>
-      <c r="V12">
-        <v>1.49</v>
-      </c>
-      <c r="W12">
-        <v>1.08</v>
-      </c>
-      <c r="X12">
-        <v>1.02</v>
-      </c>
-      <c r="Y12">
-        <v>1.2</v>
-      </c>
-      <c r="Z12">
-        <v>4.1</v>
-      </c>
-      <c r="AA12">
-        <v>1.69</v>
-      </c>
-      <c r="AB12">
-        <v>2.01</v>
-      </c>
-      <c r="AC12">
-        <v>2.75</v>
-      </c>
-      <c r="AD12">
-        <v>1.4</v>
-      </c>
       <c r="AE12">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AF12">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AG12">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.7</v>
+        <v>1.18</v>
       </c>
       <c r="AK12">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Muğlaspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,80 +2428,80 @@
         </is>
       </c>
       <c r="N13">
-        <v>4.6</v>
+        <v>2.77</v>
       </c>
       <c r="O13">
-        <v>3.7</v>
+        <v>3.38</v>
       </c>
       <c r="P13">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="Q13">
-        <v>5.37</v>
+        <v>3.75</v>
       </c>
       <c r="R13">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="S13">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T13">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U13">
-        <v>2.68</v>
+        <v>2.45</v>
       </c>
       <c r="V13">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="W13">
         <v>1.08</v>
       </c>
       <c r="X13">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z13">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AA13">
-        <v>1.89</v>
+        <v>1.69</v>
       </c>
       <c r="AB13">
-        <v>1.88</v>
+        <v>2.01</v>
       </c>
       <c r="AC13">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="AD13">
+        <v>1.4</v>
+      </c>
+      <c r="AE13">
+        <v>1.16</v>
+      </c>
+      <c r="AF13">
+        <v>1.6</v>
+      </c>
+      <c r="AG13">
+        <v>2.2</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13">
+        <v>1.7</v>
+      </c>
+      <c r="AK13">
         <v>1.3</v>
-      </c>
-      <c r="AE13">
-        <v>1.12</v>
-      </c>
-      <c r="AF13">
-        <v>1.82</v>
-      </c>
-      <c r="AG13">
-        <v>1.84</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13">
-        <v>1.18</v>
-      </c>
-      <c r="AK13">
-        <v>1.11</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="O15">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P15">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="Q15">
         <v>2.68</v>
@@ -2769,28 +2769,28 @@
         <v>2.12</v>
       </c>
       <c r="S15">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T15">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="U15">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V15">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W15">
         <v>1.05</v>
       </c>
       <c r="X15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z15">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="AA15">
         <v>1.74</v>
@@ -2808,10 +2808,10 @@
         <v>1.09</v>
       </c>
       <c r="AF15">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG15">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>

--- a/jogos_2026-10-15.xlsx
+++ b/jogos_2026-10-15.xlsx
@@ -641,7 +641,7 @@
         <v>3.5</v>
       </c>
       <c r="P2">
-        <v>1.97</v>
+        <v>2.14</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -674,10 +674,10 @@
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB2">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -1456,7 +1456,7 @@
         <v>3.46</v>
       </c>
       <c r="P7">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="Q7">
         <v>2.7</v>
@@ -1507,7 +1507,7 @@
         <v>1.7</v>
       </c>
       <c r="AG7">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1782,13 +1782,13 @@
         <v>3.5</v>
       </c>
       <c r="P9">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="Q9">
         <v>2.88</v>
       </c>
       <c r="R9">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="S9">
         <v>1.25</v>
@@ -1812,7 +1812,7 @@
         <v>1.2</v>
       </c>
       <c r="Z9">
-        <v>4.36</v>
+        <v>4.37</v>
       </c>
       <c r="AA9">
         <v>1.67</v>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O16">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="P16">
         <v>2.86</v>

--- a/jogos_2026-10-15.xlsx
+++ b/jogos_2026-10-15.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="O2">
         <v>3.5</v>
       </c>
       <c r="P2">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AA2">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB2">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1296,19 +1296,19 @@
         <v>3.2</v>
       </c>
       <c r="Q6">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="R6">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="S6">
         <v>1.4</v>
       </c>
       <c r="T6">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U6">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="V6">
         <v>1.4</v>
@@ -1320,19 +1320,19 @@
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z6">
         <v>3.3</v>
       </c>
       <c r="AA6">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AB6">
         <v>1.85</v>
       </c>
       <c r="AC6">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AD6">
         <v>1.3</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AK6">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,16 +1450,16 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="O7">
-        <v>3.46</v>
+        <v>3.57</v>
       </c>
       <c r="P7">
         <v>3.25</v>
       </c>
       <c r="Q7">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="R7">
         <v>2.1</v>
@@ -1471,7 +1471,7 @@
         <v>3</v>
       </c>
       <c r="U7">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="V7">
         <v>1.36</v>
@@ -1483,31 +1483,31 @@
         <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z7">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AA7">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AB7">
         <v>1.87</v>
       </c>
       <c r="AC7">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="AD7">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE7">
         <v>1.07</v>
       </c>
       <c r="AF7">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG7">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>1.3</v>
       </c>
       <c r="AK7">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="O8">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P8">
-        <v>1.93</v>
+        <v>2.35</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA8">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AB8">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O9">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P9">
         <v>2.59</v>
@@ -1849,7 +1849,7 @@
         <v>1.25</v>
       </c>
       <c r="AK9">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1951,7 +1951,7 @@
         <v>5.1</v>
       </c>
       <c r="R10">
-        <v>2.58</v>
+        <v>2.51</v>
       </c>
       <c r="S10">
         <v>1.17</v>
@@ -1963,7 +1963,7 @@
         <v>2</v>
       </c>
       <c r="V10">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="W10">
         <v>1.17</v>
@@ -1984,10 +1984,10 @@
         <v>2.74</v>
       </c>
       <c r="AC10">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AD10">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AE10">
         <v>1.36</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AK10">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2117,7 +2117,7 @@
         <v>2.12</v>
       </c>
       <c r="S11">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T11">
         <v>2.95</v>
@@ -2138,13 +2138,13 @@
         <v>1.23</v>
       </c>
       <c r="Z11">
-        <v>3.58</v>
+        <v>3.62</v>
       </c>
       <c r="AA11">
         <v>1.81</v>
       </c>
       <c r="AB11">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AC11">
         <v>2.97</v>
@@ -2153,7 +2153,7 @@
         <v>1.3</v>
       </c>
       <c r="AE11">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF11">
         <v>1.64</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AK11">
         <v>1.4</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Muğlaspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,80 +2265,80 @@
         </is>
       </c>
       <c r="N12">
-        <v>4.6</v>
+        <v>2.71</v>
       </c>
       <c r="O12">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="P12">
+        <v>2</v>
+      </c>
+      <c r="Q12">
+        <v>3.75</v>
+      </c>
+      <c r="R12">
+        <v>2.19</v>
+      </c>
+      <c r="S12">
+        <v>1.3</v>
+      </c>
+      <c r="T12">
+        <v>3.2</v>
+      </c>
+      <c r="U12">
+        <v>2.45</v>
+      </c>
+      <c r="V12">
+        <v>1.49</v>
+      </c>
+      <c r="W12">
+        <v>1.08</v>
+      </c>
+      <c r="X12">
+        <v>1.02</v>
+      </c>
+      <c r="Y12">
+        <v>1.2</v>
+      </c>
+      <c r="Z12">
+        <v>4.1</v>
+      </c>
+      <c r="AA12">
+        <v>1.69</v>
+      </c>
+      <c r="AB12">
+        <v>2.01</v>
+      </c>
+      <c r="AC12">
+        <v>2.8</v>
+      </c>
+      <c r="AD12">
+        <v>1.4</v>
+      </c>
+      <c r="AE12">
+        <v>1.16</v>
+      </c>
+      <c r="AF12">
         <v>1.6</v>
       </c>
-      <c r="Q12">
-        <v>5.37</v>
-      </c>
-      <c r="R12">
+      <c r="AG12">
         <v>2.2</v>
       </c>
-      <c r="S12">
-        <v>1.33</v>
-      </c>
-      <c r="T12">
-        <v>3</v>
-      </c>
-      <c r="U12">
-        <v>2.68</v>
-      </c>
-      <c r="V12">
-        <v>1.37</v>
-      </c>
-      <c r="W12">
-        <v>1.1</v>
-      </c>
-      <c r="X12">
-        <v>1.03</v>
-      </c>
-      <c r="Y12">
-        <v>1.25</v>
-      </c>
-      <c r="Z12">
-        <v>3.6</v>
-      </c>
-      <c r="AA12">
-        <v>1.89</v>
-      </c>
-      <c r="AB12">
-        <v>1.88</v>
-      </c>
-      <c r="AC12">
-        <v>3.2</v>
-      </c>
-      <c r="AD12">
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12">
+        <v>1.7</v>
+      </c>
+      <c r="AK12">
         <v>1.3</v>
-      </c>
-      <c r="AE12">
-        <v>1.12</v>
-      </c>
-      <c r="AF12">
-        <v>1.82</v>
-      </c>
-      <c r="AG12">
-        <v>1.84</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12">
-        <v>1.18</v>
-      </c>
-      <c r="AK12">
-        <v>1.13</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Muğlaspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.77</v>
+        <v>4.6</v>
       </c>
       <c r="O13">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="P13">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="Q13">
-        <v>3.75</v>
+        <v>5.37</v>
       </c>
       <c r="R13">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="S13">
+        <v>1.33</v>
+      </c>
+      <c r="T13">
+        <v>3</v>
+      </c>
+      <c r="U13">
+        <v>2.68</v>
+      </c>
+      <c r="V13">
+        <v>1.37</v>
+      </c>
+      <c r="W13">
+        <v>1.1</v>
+      </c>
+      <c r="X13">
+        <v>1.03</v>
+      </c>
+      <c r="Y13">
+        <v>1.25</v>
+      </c>
+      <c r="Z13">
+        <v>3.6</v>
+      </c>
+      <c r="AA13">
+        <v>1.9</v>
+      </c>
+      <c r="AB13">
+        <v>1.92</v>
+      </c>
+      <c r="AC13">
+        <v>3.2</v>
+      </c>
+      <c r="AD13">
         <v>1.3</v>
       </c>
-      <c r="T13">
-        <v>3.2</v>
-      </c>
-      <c r="U13">
-        <v>2.45</v>
-      </c>
-      <c r="V13">
-        <v>1.49</v>
-      </c>
-      <c r="W13">
-        <v>1.08</v>
-      </c>
-      <c r="X13">
-        <v>1.02</v>
-      </c>
-      <c r="Y13">
-        <v>1.2</v>
-      </c>
-      <c r="Z13">
-        <v>4.1</v>
-      </c>
-      <c r="AA13">
-        <v>1.69</v>
-      </c>
-      <c r="AB13">
-        <v>2.01</v>
-      </c>
-      <c r="AC13">
-        <v>2.8</v>
-      </c>
-      <c r="AD13">
-        <v>1.4</v>
-      </c>
       <c r="AE13">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AF13">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AG13">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.7</v>
+        <v>1.18</v>
       </c>
       <c r="AK13">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2926,10 +2926,10 @@
         <v>2.86</v>
       </c>
       <c r="Q16">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="R16">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="S16">
         <v>1.3</v>
@@ -2962,7 +2962,7 @@
         <v>2.05</v>
       </c>
       <c r="AC16">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="AD16">
         <v>1.4</v>
@@ -2974,7 +2974,7 @@
         <v>1.6</v>
       </c>
       <c r="AG16">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>1.23</v>
       </c>
       <c r="AK16">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL16">
         <v>0</v>

--- a/jogos_2026-10-15.xlsx
+++ b/jogos_2026-10-15.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="O2">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P2">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="Q2">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="R2">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="S2">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T2">
-        <v>2.95</v>
+        <v>2.79</v>
       </c>
       <c r="U2">
-        <v>2.58</v>
+        <v>3.13</v>
       </c>
       <c r="V2">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="W2">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z2">
-        <v>3.48</v>
+        <v>3.05</v>
       </c>
       <c r="AA2">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AB2">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AC2">
-        <v>3.05</v>
+        <v>3.73</v>
       </c>
       <c r="AD2">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE2">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF2">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="AG2">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.27</v>
+        <v>1.53</v>
       </c>
       <c r="AK2">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>2.53</v>
       </c>
       <c r="R6">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="S6">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="T6">
         <v>2.88</v>
@@ -1320,7 +1320,7 @@
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z6">
         <v>3.3</v>
@@ -1450,19 +1450,19 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="O7">
-        <v>3.57</v>
+        <v>3.47</v>
       </c>
       <c r="P7">
         <v>3.25</v>
       </c>
       <c r="Q7">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="R7">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S7">
         <v>1.33</v>
@@ -1474,7 +1474,7 @@
         <v>2.6</v>
       </c>
       <c r="V7">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W7">
         <v>1.06</v>
@@ -1483,47 +1483,47 @@
         <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z7">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AA7">
         <v>1.82</v>
       </c>
       <c r="AB7">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AC7">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="AD7">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE7">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF7">
+        <v>1.65</v>
+      </c>
+      <c r="AG7">
+        <v>2.1</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
+        <v>1.33</v>
+      </c>
+      <c r="AK7">
         <v>1.67</v>
-      </c>
-      <c r="AG7">
-        <v>2</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>1.3</v>
-      </c>
-      <c r="AK7">
-        <v>1.75</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,46 +1613,46 @@
         </is>
       </c>
       <c r="N8">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="O8">
         <v>3.1</v>
       </c>
       <c r="P8">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q8">
         <v>3.86</v>
       </c>
       <c r="R8">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="S8">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T8">
-        <v>2.51</v>
+        <v>2.75</v>
       </c>
       <c r="U8">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="V8">
         <v>1.32</v>
       </c>
       <c r="W8">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X8">
         <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z8">
-        <v>2.92</v>
+        <v>3.06</v>
       </c>
       <c r="AA8">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="AB8">
         <v>1.67</v>
@@ -1776,19 +1776,19 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="O9">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P9">
         <v>2.59</v>
       </c>
       <c r="Q9">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="R9">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="S9">
         <v>1.25</v>
@@ -1800,7 +1800,7 @@
         <v>2.4</v>
       </c>
       <c r="V9">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W9">
         <v>1.1</v>
@@ -1815,10 +1815,10 @@
         <v>4.37</v>
       </c>
       <c r="AA9">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB9">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AC9">
         <v>2.59</v>
@@ -1827,13 +1827,13 @@
         <v>1.44</v>
       </c>
       <c r="AE9">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF9">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG9">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>1.25</v>
       </c>
       <c r="AK9">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,16 +1939,16 @@
         </is>
       </c>
       <c r="N10">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O10">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="P10">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="Q10">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="R10">
         <v>2.51</v>
@@ -1963,25 +1963,25 @@
         <v>2</v>
       </c>
       <c r="V10">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="W10">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X10">
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z10">
-        <v>5.7</v>
+        <v>6.05</v>
       </c>
       <c r="AA10">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AB10">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AC10">
         <v>1.98</v>
@@ -1993,10 +1993,10 @@
         <v>1.36</v>
       </c>
       <c r="AF10">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AG10">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AK11">
         <v>1.4</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Muğlaspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.71</v>
+        <v>4.6</v>
       </c>
       <c r="O12">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="P12">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="Q12">
-        <v>3.75</v>
+        <v>5.37</v>
       </c>
       <c r="R12">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="S12">
+        <v>1.33</v>
+      </c>
+      <c r="T12">
+        <v>3</v>
+      </c>
+      <c r="U12">
+        <v>2.68</v>
+      </c>
+      <c r="V12">
+        <v>1.37</v>
+      </c>
+      <c r="W12">
+        <v>1.1</v>
+      </c>
+      <c r="X12">
+        <v>1.03</v>
+      </c>
+      <c r="Y12">
+        <v>1.25</v>
+      </c>
+      <c r="Z12">
+        <v>3.6</v>
+      </c>
+      <c r="AA12">
+        <v>1.91</v>
+      </c>
+      <c r="AB12">
+        <v>1.92</v>
+      </c>
+      <c r="AC12">
+        <v>3.2</v>
+      </c>
+      <c r="AD12">
         <v>1.3</v>
       </c>
-      <c r="T12">
-        <v>3.2</v>
-      </c>
-      <c r="U12">
-        <v>2.45</v>
-      </c>
-      <c r="V12">
-        <v>1.49</v>
-      </c>
-      <c r="W12">
-        <v>1.08</v>
-      </c>
-      <c r="X12">
-        <v>1.02</v>
-      </c>
-      <c r="Y12">
-        <v>1.2</v>
-      </c>
-      <c r="Z12">
-        <v>4.1</v>
-      </c>
-      <c r="AA12">
-        <v>1.69</v>
-      </c>
-      <c r="AB12">
-        <v>2.01</v>
-      </c>
-      <c r="AC12">
-        <v>2.8</v>
-      </c>
-      <c r="AD12">
-        <v>1.4</v>
-      </c>
       <c r="AE12">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AF12">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AG12">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.7</v>
+        <v>1.18</v>
       </c>
       <c r="AK12">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Muğlaspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,80 +2428,80 @@
         </is>
       </c>
       <c r="N13">
-        <v>4.6</v>
+        <v>2.71</v>
       </c>
       <c r="O13">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="P13">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="Q13">
-        <v>5.37</v>
+        <v>3.75</v>
       </c>
       <c r="R13">
         <v>2.2</v>
       </c>
       <c r="S13">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T13">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U13">
-        <v>2.68</v>
+        <v>2.45</v>
       </c>
       <c r="V13">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="W13">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X13">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z13">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AA13">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AB13">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="AC13">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="AD13">
+        <v>1.4</v>
+      </c>
+      <c r="AE13">
+        <v>1.17</v>
+      </c>
+      <c r="AF13">
+        <v>1.6</v>
+      </c>
+      <c r="AG13">
+        <v>2.2</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13">
+        <v>1.7</v>
+      </c>
+      <c r="AK13">
         <v>1.3</v>
-      </c>
-      <c r="AE13">
-        <v>1.12</v>
-      </c>
-      <c r="AF13">
-        <v>1.82</v>
-      </c>
-      <c r="AG13">
-        <v>1.91</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13">
-        <v>1.18</v>
-      </c>
-      <c r="AK13">
-        <v>1.13</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="O15">
         <v>3.3</v>
       </c>
       <c r="P15">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="Q15">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="R15">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="S15">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T15">
-        <v>2.94</v>
+        <v>3.28</v>
       </c>
       <c r="U15">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="V15">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="W15">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X15">
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="Z15">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="AA15">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AB15">
-        <v>1.94</v>
+        <v>2.4</v>
       </c>
       <c r="AC15">
-        <v>2.83</v>
+        <v>2.4</v>
       </c>
       <c r="AD15">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AE15">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AF15">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AG15">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK15">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2920,28 +2920,28 @@
         <v>2.2</v>
       </c>
       <c r="O16">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P16">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="Q16">
         <v>2.8</v>
       </c>
       <c r="R16">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="S16">
         <v>1.3</v>
       </c>
       <c r="T16">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="U16">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="V16">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W16">
         <v>1.08</v>
@@ -2962,7 +2962,7 @@
         <v>2.05</v>
       </c>
       <c r="AC16">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="AD16">
         <v>1.4</v>
@@ -2974,7 +2974,7 @@
         <v>1.6</v>
       </c>
       <c r="AG16">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AK16">
         <v>1.57</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q17">
         <v>0</v>

--- a/jogos_2026-10-15.xlsx
+++ b/jogos_2026-10-15.xlsx
@@ -612,26 +612,26 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
@@ -696,12 +696,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7", "45+4", "85"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["19", "45"]</t>
         </is>
       </c>
       <c r="AJ2">
@@ -714,28 +714,28 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -778,13 +778,13 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -794,32 +794,32 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="O3">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P3">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="Q3">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R3">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S3">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T3">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="U3">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="V3">
         <v>1.36</v>
@@ -828,25 +828,25 @@
         <v>1.07</v>
       </c>
       <c r="X3">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z3">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="AA3">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="AB3">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC3">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="AD3">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE3">
         <v>1.06</v>
@@ -864,41 +864,41 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["38"]</t>
         </is>
       </c>
       <c r="AJ3">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK3">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -953,66 +953,66 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
         <v>5.46</v>
       </c>
       <c r="O4">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="P4">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="Q4">
-        <v>6.05</v>
+        <v>5.8</v>
       </c>
       <c r="R4">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="S4">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T4">
         <v>3.25</v>
       </c>
       <c r="U4">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="V4">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="W4">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
         <v>1.18</v>
       </c>
       <c r="Z4">
-        <v>3.86</v>
+        <v>4.1</v>
       </c>
       <c r="AA4">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AB4">
         <v>2.1</v>
       </c>
       <c r="AC4">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="AD4">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AE4">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF4">
         <v>1.75</v>
@@ -1027,41 +1027,41 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["85"]</t>
         </is>
       </c>
       <c r="AJ4">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AK4">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>0.59</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1101,91 +1101,91 @@
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
         <v>1.12</v>
       </c>
       <c r="O5">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="P5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q5">
         <v>1.36</v>
       </c>
       <c r="R5">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="S5">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T5">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="U5">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="V5">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="W5">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
         <v>1.07</v>
       </c>
       <c r="Z5">
-        <v>6.45</v>
+        <v>5.25</v>
       </c>
       <c r="AA5">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AB5">
-        <v>3.25</v>
+        <v>2.79</v>
       </c>
       <c r="AC5">
-        <v>1.76</v>
+        <v>2.01</v>
       </c>
       <c r="AD5">
-        <v>1.92</v>
+        <v>1.69</v>
       </c>
       <c r="AE5">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="AF5">
-        <v>2.03</v>
+        <v>2.27</v>
       </c>
       <c r="AG5">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["9", "12", "45+2", "86"]</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1197,34 +1197,34 @@
         <v>1.01</v>
       </c>
       <c r="AK5">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1264,13 +1264,13 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10"]</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -1366,28 +1366,28 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1439,14 +1439,14 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["52", "80"]</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -1529,28 +1529,28 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -1602,14 +1602,14 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["89"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -1692,28 +1692,28 @@
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1753,26 +1753,26 @@
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17", "49"]</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["27", "88", "90+5"]</t>
         </is>
       </c>
       <c r="AJ9">
@@ -1855,28 +1855,28 @@
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -1916,26 +1916,26 @@
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13"]</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["20", "54", "72"]</t>
         </is>
       </c>
       <c r="AJ10">
@@ -2018,28 +2018,28 @@
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>1.64</v>
       </c>
       <c r="AG11">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AK11">
         <v>1.4</v>
@@ -2271,16 +2271,16 @@
         <v>3.6</v>
       </c>
       <c r="P12">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="Q12">
-        <v>5.37</v>
+        <v>5.58</v>
       </c>
       <c r="R12">
         <v>2.2</v>
       </c>
       <c r="S12">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T12">
         <v>3</v>
@@ -2292,7 +2292,7 @@
         <v>1.37</v>
       </c>
       <c r="W12">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X12">
         <v>1.03</v>
@@ -2304,22 +2304,22 @@
         <v>3.6</v>
       </c>
       <c r="AA12">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AB12">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AC12">
         <v>3.2</v>
       </c>
       <c r="AD12">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE12">
         <v>1.12</v>
       </c>
       <c r="AF12">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AG12">
         <v>1.91</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK12">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2431,7 +2431,7 @@
         <v>2.71</v>
       </c>
       <c r="O13">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="P13">
         <v>2</v>
@@ -2458,7 +2458,7 @@
         <v>1.08</v>
       </c>
       <c r="X13">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
         <v>1.2</v>
@@ -2473,7 +2473,7 @@
         <v>2.01</v>
       </c>
       <c r="AC13">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AD13">
         <v>1.4</v>
@@ -2482,7 +2482,7 @@
         <v>1.17</v>
       </c>
       <c r="AF13">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG13">
         <v>2.2</v>
@@ -2501,7 +2501,7 @@
         <v>1.7</v>
       </c>
       <c r="AK13">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="O16">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P16">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="Q16">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="R16">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="S16">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T16">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U16">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="V16">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="W16">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X16">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z16">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA16">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AB16">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AC16">
-        <v>2.91</v>
+        <v>2.59</v>
       </c>
       <c r="AD16">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE16">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF16">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AG16">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
         <v>1.57</v>

--- a/jogos_2026-10-15.xlsx
+++ b/jogos_2026-10-15.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU19"/>
+  <dimension ref="A1:AU18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -2091,14 +2091,14 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["78"]</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["48", "66", "75"]</t>
         </is>
       </c>
       <c r="AJ11">
@@ -2181,28 +2181,28 @@
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -2257,11 +2257,11 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["58", "79", "83"]</t>
         </is>
       </c>
       <c r="AJ12">
@@ -2344,28 +2344,28 @@
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -2417,14 +2417,14 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["80"]</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+6"]</t>
         </is>
       </c>
       <c r="AJ13">
@@ -2507,28 +2507,28 @@
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2731,42 +2731,42 @@
         </is>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15">
         <v>0</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
         <v>1.97</v>
       </c>
       <c r="O15">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P15">
         <v>2.75</v>
       </c>
       <c r="Q15">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="R15">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S15">
         <v>1.25</v>
@@ -2805,7 +2805,7 @@
         <v>1.5</v>
       </c>
       <c r="AE15">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF15">
         <v>1.44</v>
@@ -2815,46 +2815,46 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["83", "88"]</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["39"]</t>
         </is>
       </c>
       <c r="AJ15">
         <v>1.29</v>
       </c>
       <c r="AK15">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AN15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="AP15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -2894,26 +2894,26 @@
         </is>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
@@ -2978,12 +2978,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["82"]</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["34"]</t>
         </is>
       </c>
       <c r="AJ16">
@@ -2996,28 +2996,28 @@
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2026-10-15 17:30:00</t>
+          <t>2026-10-15 21:00:00</t>
         </is>
       </c>
     </row>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Gamo Chencha</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G18">
@@ -3346,169 +3346,6 @@
         <v>0</v>
       </c>
       <c r="AU18" t="inlineStr">
-        <is>
-          <t>2026-10-15 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ethiopia Ethiopia Premier League</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Gamo Chencha</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Sidama Bunna</t>
-        </is>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19">
-        <v>0</v>
-      </c>
-      <c r="P19">
-        <v>0</v>
-      </c>
-      <c r="Q19">
-        <v>0</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
-        <v>0</v>
-      </c>
-      <c r="T19">
-        <v>0</v>
-      </c>
-      <c r="U19">
-        <v>0</v>
-      </c>
-      <c r="V19">
-        <v>0</v>
-      </c>
-      <c r="W19">
-        <v>0</v>
-      </c>
-      <c r="X19">
-        <v>0</v>
-      </c>
-      <c r="Y19">
-        <v>0</v>
-      </c>
-      <c r="Z19">
-        <v>0</v>
-      </c>
-      <c r="AA19">
-        <v>0</v>
-      </c>
-      <c r="AB19">
-        <v>0</v>
-      </c>
-      <c r="AC19">
-        <v>0</v>
-      </c>
-      <c r="AD19">
-        <v>0</v>
-      </c>
-      <c r="AE19">
-        <v>0</v>
-      </c>
-      <c r="AF19">
-        <v>0</v>
-      </c>
-      <c r="AG19">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19">
-        <v>0</v>
-      </c>
-      <c r="AK19">
-        <v>0</v>
-      </c>
-      <c r="AL19">
-        <v>0</v>
-      </c>
-      <c r="AM19">
-        <v>-1</v>
-      </c>
-      <c r="AN19">
-        <v>-1</v>
-      </c>
-      <c r="AO19">
-        <v>-1</v>
-      </c>
-      <c r="AP19">
-        <v>-1</v>
-      </c>
-      <c r="AQ19">
-        <v>0</v>
-      </c>
-      <c r="AR19">
-        <v>0</v>
-      </c>
-      <c r="AS19">
-        <v>0</v>
-      </c>
-      <c r="AT19">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
         <is>
           <t>2026-10-15 21:00:00</t>
         </is>
